--- a/auditoria-transformadores-134/public/bases/Base_Funis.xlsx
+++ b/auditoria-transformadores-134/public/bases/Base_Funis.xlsx
@@ -3422,7 +3422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -3435,7 +3435,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>240 exclusões em 25 categorias, e elas se dividem em duas famílias que convém não misturar: 137 não têm interrupção que sustente o caso e 103 têm causa ou documento fora do indicador.</t>
+          <t>240 exclusões em 24 categorias, e elas se dividem em duas famílias que convém não misturar: 137 não têm interrupção que sustente o caso e 103 têm causa ou documento fora do indicador.</t>
         </is>
       </c>
     </row>
@@ -3685,11 +3685,11 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -4068,31 +4068,6 @@
         </is>
       </c>
       <c r="E27" t="inlineStr">
-        <is>
-          <t>causa ou documento fora do indicador</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Obra de poste — segurança</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>seguranca</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
         <is>
           <t>causa ou documento fora do indicador</t>
         </is>
@@ -5738,7 +5713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6167,6 +6142,33 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ETO-RD-GU 00685/2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>EXCLUIR</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Abalroamento</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EXCLUÍDA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>o dono mandou mover para abalroamento, e as quatro vozes concordam com ele: a Crítica registra causa POSTE DE AT e subcausa ABALROADO, o TMAE repete as duas, a SS foi gravada como ABALROAMENTO e a obra 0412600528 entra no SIGCO 20497 — DANOS CAUSADOS POR TERCEIROS. O caso saía como obra de poste por segurança, que é outra coisa: segurança é a companhia decidindo trocar um poste, abalroamento é um terceiro derrubando. A diferença muda para onde o custo vai — ressarcimento, não manutenção</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>

--- a/auditoria-transformadores-134/public/bases/Base_Funis.xlsx
+++ b/auditoria-transformadores-134/public/bases/Base_Funis.xlsx
@@ -3422,7 +3422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -3435,7 +3435,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>240 exclusões em 24 categorias, e elas se dividem em duas famílias que convém não misturar: 137 não têm interrupção que sustente o caso e 103 têm causa ou documento fora do indicador.</t>
+          <t>240 exclusões em 23 categorias, e elas se dividem em duas famílias que convém não misturar: 137 não têm interrupção que sustente o caso e 103 têm causa ou documento fora do indicador.</t>
         </is>
       </c>
     </row>
@@ -3485,11 +3485,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3510,11 +3510,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3601,12 +3601,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sem interrupção na base Crítica</t>
+          <t>Tape interno</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sem_fato</t>
+          <t>tap</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -3619,27 +3619,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>sem interrupção que sustente</t>
+          <t>causa ou documento fora do indicador</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tape interno</t>
+          <t>Sem OS e sem obra</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>tap</t>
+          <t>sem_os</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3651,12 +3651,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sem OS e sem obra</t>
+          <t>Abalroamento</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sem_os</t>
+          <t>abalroamento</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -3676,20 +3676,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Abalroamento</t>
+          <t>Obra encerrada sem transformador</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>abalroamento</t>
+          <t>obra_sem_transformador</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3701,20 +3701,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Obra encerrada sem transformador</t>
+          <t>Preventivo ou programado</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>obra_sem_transformador</t>
+          <t>preventivo</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3726,20 +3726,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Preventivo ou programado</t>
+          <t>Falta de fase interna</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>preventivo</t>
+          <t>falta_fase</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3751,12 +3751,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Falta de fase interna</t>
+          <t>Auxiliar de religador ou regulador</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>falta_fase</t>
+          <t>auxiliar</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3776,12 +3776,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Auxiliar de religador ou regulador</t>
+          <t>Divisão de circuito</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>auxiliar</t>
+          <t>divisao</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3801,12 +3801,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Divisão de circuito</t>
+          <t>Cola e fita — reparo, não troca</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>divisao</t>
+          <t>cola_fita</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3826,12 +3826,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cola e fita — reparo, não troca</t>
+          <t>Desativação do posto</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>cola_fita</t>
+          <t>desativacao</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3851,20 +3851,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Desativação do posto</t>
+          <t>Obra aberta que não executou nada</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>desativacao</t>
+          <t>obra_sem_execucao</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3876,12 +3876,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Obra aberta que não executou nada</t>
+          <t>Causada por terceiros</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>obra_sem_execucao</t>
+          <t>terceiros</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3901,12 +3901,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Causada por terceiros</t>
+          <t>Possível erro de cadastro do código</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>terceiros</t>
+          <t>erro_cadastro</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3926,12 +3926,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Possível erro de cadastro do código</t>
+          <t>Avaliar com o Matheus</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>erro_cadastro</t>
+          <t>avaliar_matheus</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3951,12 +3951,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Avaliar com o Matheus</t>
+          <t>Transformador particular</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>avaliar_matheus</t>
+          <t>particular</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3976,12 +3976,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Transformador particular</t>
+          <t>Construção ou obra nova</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>particular</t>
+          <t>construcao</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -4001,12 +4001,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Construção ou obra nova</t>
+          <t>A obra trocou chave fusível</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>construcao</t>
+          <t>obra_chave</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4026,12 +4026,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A obra trocou chave fusível</t>
+          <t>SS duplicada</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>obra_chave</t>
+          <t>duplicada</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -4043,31 +4043,6 @@
         </is>
       </c>
       <c r="E26" t="inlineStr">
-        <is>
-          <t>causa ou documento fora do indicador</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>SS duplicada</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>duplicada</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
         <is>
           <t>causa ou documento fora do indicador</t>
         </is>
@@ -4131,7 +4106,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4146,7 +4121,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -4161,7 +4136,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/auditoria-transformadores-134/public/bases/Base_Funis.xlsx
+++ b/auditoria-transformadores-134/public/bases/Base_Funis.xlsx
@@ -3476,20 +3476,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ausente da base · registro em outra data</t>
+          <t>Ausente da base de interrupções</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fora_da_janela</t>
+          <t>sem_interrupcao</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3501,20 +3501,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ausente da base de interrupções</t>
+          <t>Ausente da base · registro em outra data</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sem_interrupcao</t>
+          <t>fora_da_janela</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/auditoria-transformadores-134/public/bases/Base_Funis.xlsx
+++ b/auditoria-transformadores-134/public/bases/Base_Funis.xlsx
@@ -526,10 +526,10 @@
         <v>1510</v>
       </c>
       <c r="D5" t="n">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="E5" t="n">
-        <v>1270</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="6">
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1270</v>
+        <v>1289</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1270</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="7">
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1270</v>
+        <v>1289</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1270</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="8">
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1270</v>
+        <v>1289</v>
       </c>
       <c r="D8" t="n">
         <v>21</v>
       </c>
       <c r="E8" t="n">
-        <v>1249</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="9">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1249</v>
+        <v>1268</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1249</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="10">
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1249</v>
+        <v>1268</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1249</v>
+        <v>1268</v>
       </c>
     </row>
   </sheetData>
@@ -651,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E138"/>
+  <dimension ref="A1:E139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -724,39 +724,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARAGUAINA</t>
+          <t>PORTO NACIONAL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PORTO NACIONAL</t>
+          <t>ARAGUAINA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -800,11 +800,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MONTE DO CARMO</t>
+          <t>PARANA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -813,26 +813,26 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PARANA</t>
+          <t>MONTE DO CARMO</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -1180,45 +1180,45 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PINDORAMA DO TOCANTINS</t>
+          <t>COLMEIA</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>14</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SAO VALERIO</t>
+          <t>PINDORAMA DO TOCANTINS</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>14</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DUERE</t>
+          <t>SAO VALERIO</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1237,39 +1237,39 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SANTA ROSA DO TOCANTINS</t>
+          <t>DUERE</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>14</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>COLMEIA</t>
+          <t>SANTA ROSA DO TOCANTINS</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
@@ -1313,26 +1313,26 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>VILA LUZIMANGUES</t>
+          <t>MARIANOPOLIS DO TOCANTINS</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>12</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MIRANORTE</t>
+          <t>VILA LUZIMANGUES</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1342,67 +1342,67 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>WANDERLANDIA</t>
+          <t>MIRANORTE</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>12</v>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NOVA OLINDA</t>
+          <t>WANDERLANDIA</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>12</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MARIANOPOLIS DO TOCANTINS</t>
+          <t>NOVA OLINDA</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
@@ -1655,102 +1655,102 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PARAISO DO TOCANTINS</t>
+          <t>LIZARDA</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>9</v>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CRISTALANDIA</t>
+          <t>PARAISO DO TOCANTINS</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>9</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DARCINOPOLIS</t>
+          <t>CRISTALANDIA</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ALIANCA DO TOCANTINS</t>
+          <t>DARCINOPOLIS</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>8</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CASEARA</t>
+          <t>ALIANCA DO TOCANTINS</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>8</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PALMEIRANTE</t>
+          <t>CASEARA</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1769,7 +1769,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LIZARDA</t>
+          <t>PALMEIRANTE</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1788,45 +1788,45 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MONTE SANTO DO TOCANTINS</t>
+          <t>MURICILANDIA</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>8</v>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LAGOA DA CONFUSAO</t>
+          <t>MONTE SANTO DO TOCANTINS</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>8</v>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ARAGUANA</t>
+          <t>CAMPOS LINDOS</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1845,45 +1845,45 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IPUEIRAS</t>
+          <t>LAGOA DA CONFUSAO</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LAJEADO</t>
+          <t>ARAGUANA</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TUPIRATINS</t>
+          <t>IPUEIRAS</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1902,102 +1902,102 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ITAPIRATINS</t>
+          <t>LAJEADO</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>7</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CONCEICAO DO TOCANTINS</t>
+          <t>TUPIRATINS</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>7</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CAMPOS LINDOS</t>
+          <t>RECURSOLANDIA</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>7</v>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FILADELFIA</t>
+          <t>ITAPIRATINS</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>7</v>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t>PALMEIROPOLIS</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>7</v>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FIGUEIROPOLIS</t>
+          <t>CONCEICAO DO TOCANTINS</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -2016,55 +2016,55 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PONTE ALTA DO BOM JESUS</t>
+          <t>FILADELFIA</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PRESIDENTE KENNEDY</t>
+          <t>FATIMA</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TALISMA</t>
+          <t>FIGUEIROPOLIS</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
         <v>7</v>
@@ -2073,7 +2073,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CHAPADA DE AREIA</t>
+          <t>PONTE ALTA DO BOM JESUS</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -2092,163 +2092,163 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AUGUSTINOPOLIS</t>
+          <t>PRESIDENTE KENNEDY</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>6</v>
       </c>
       <c r="C77" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MURICILANDIA</t>
+          <t>TALISMA</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>6</v>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PALMEIROPOLIS</t>
+          <t>CHAPADA DE AREIA</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>6</v>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TOCANTINOPOLIS</t>
+          <t>AUGUSTINOPOLIS</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>6</v>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PALMEIRAS DO TOCANTINS</t>
+          <t>TOCANTINOPOLIS</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>6</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PAU D'ARCO</t>
+          <t>PALMEIRAS DO TOCANTINS</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>6</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SAO MIGUEL DO TOCANTINS</t>
+          <t>PAU D'ARCO</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>6</v>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CENTENARIO</t>
+          <t>XAMBIOA</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>RECURSOLANDIA</t>
+          <t>SAO MIGUEL DO TOCANTINS</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C85" t="n">
         <v>3</v>
@@ -2257,32 +2257,32 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ANGICO</t>
+          <t>CENTENARIO</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>5</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CRIXÁS DO TOCANTINS</t>
+          <t>ANGICO</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -2301,7 +2301,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DIANOPOLIS</t>
+          <t>CRIXÁS DO TOCANTINS</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -2320,153 +2320,153 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>NOVA ROSALANDIA</t>
+          <t>DIANOPOLIS</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>5</v>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BANDEIRANTES DO TOCANTINS</t>
+          <t>NOVA ROSALANDIA</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>5</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PIRAQUE</t>
+          <t>BANDEIRANTES DO TOCANTINS</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>5</v>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CARIRI DO TOCANTINS</t>
+          <t>PIRAQUE</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>5</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BARRA DO OURO</t>
+          <t>CARIRI DO TOCANTINS</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>5</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ARAPOEMA</t>
+          <t>BARRA DO OURO</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>5</v>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PEDRO AFONSO</t>
+          <t>ARAPOEMA</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>5</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>XAMBIOA</t>
+          <t>PEDRO AFONSO</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>5</v>
       </c>
       <c r="C96" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97">
@@ -3118,7 +3118,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SAO SEBASTIAO DO TOCANTINS</t>
+          <t>RIO DA CONCEICAO</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -3137,64 +3137,64 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FORTALEZA DO TABOCAO</t>
+          <t>SAO SEBASTIAO DO TOCANTINS</t>
         </is>
       </c>
       <c r="B132" t="n">
         <v>1</v>
       </c>
       <c r="C132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
       </c>
       <c r="E132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>COMBINADO</t>
+          <t>FORTALEZA DO TABOCAO</t>
         </is>
       </c>
       <c r="B133" t="n">
         <v>1</v>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>NOVO ALEGRE</t>
+          <t>COMBINADO</t>
         </is>
       </c>
       <c r="B134" t="n">
         <v>1</v>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
       </c>
       <c r="E134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CARMOLANDIA</t>
+          <t>NOVO ALEGRE</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -3213,7 +3213,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MAURILANDIA DO TOCANTINS</t>
+          <t>CARMOLANDIA</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -3232,7 +3232,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AURORA DO TOCANTINS</t>
+          <t>MAURILANDIA DO TOCANTINS</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -3251,19 +3251,38 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
+          <t>AURORA DO TOCANTINS</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
           <t>ANANAS</t>
         </is>
       </c>
-      <c r="B138" t="n">
-        <v>1</v>
-      </c>
-      <c r="C138" t="n">
-        <v>1</v>
-      </c>
-      <c r="D138" t="n">
-        <v>0</v>
-      </c>
-      <c r="E138" t="n">
+      <c r="B139" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3325,11 +3344,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1186</v>
+        <v>1205</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>79.8%</t>
         </is>
       </c>
     </row>
@@ -3355,11 +3374,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1249</v>
+        <v>1268</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>84.0%</t>
         </is>
       </c>
     </row>
@@ -3370,11 +3389,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>14.6%</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3454,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>240 exclusões em 23 categorias, e elas se dividem em duas famílias que convém não misturar: 137 não têm interrupção que sustente o caso e 103 têm causa ou documento fora do indicador.</t>
+          <t>221 exclusões em 23 categorias, e elas se dividem em duas famílias que convém não misturar: 118 não têm interrupção que sustente o caso e 103 têm causa ou documento fora do indicador.</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3508,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3510,11 +3529,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3539,7 +3558,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3564,7 +3583,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3589,7 +3608,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3614,7 +3633,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3639,7 +3658,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3664,7 +3683,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3689,7 +3708,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3714,7 +3733,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3739,7 +3758,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3764,7 +3783,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3789,7 +3808,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3814,7 +3833,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3839,7 +3858,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3864,7 +3883,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3889,7 +3908,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3914,7 +3933,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3939,7 +3958,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3964,7 +3983,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3989,7 +4008,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4014,7 +4033,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4039,7 +4058,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4121,7 +4140,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -4151,7 +4170,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -4233,7 +4252,7 @@
         <v>123</v>
       </c>
       <c r="C5" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -5204,7 +5223,7 @@
         <v>61</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -5298,7 +5317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5314,7 +5333,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>8 transformadores saíram mais de uma vez no semestre, somando 16 solicitações — que já estão contadas na saída, não se somam por fora. Quando as ocorrências são distintas e cada uma tem material próprio, são dois eventos reais e não erro de contagem.</t>
+          <t>9 transformadores saíram mais de uma vez no semestre, somando 18 solicitações — que já estão contadas na saída, não se somam por fora. Quando as ocorrências são distintas e cada uma tem material próprio, são dois eventos reais e não erro de contagem.</t>
         </is>
       </c>
     </row>
@@ -5449,28 +5468,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5713428152</t>
+          <t>5744418082</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SANTA ROSA DO TOCANTINS</t>
+          <t>LIZARDA</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DG-RD-PO 00073/2026 · DG-RD-PO 00167/2026</t>
+          <t>DOLP-RD-PA 00101/2026 · DOLP-RD-PA 00182/2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20264088317207 · 20264117832489</t>
+          <t>20264090305646 · 20264116126348</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5487,28 +5506,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5733283256</t>
+          <t>5713428152</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MATEIROS</t>
+          <t>SANTA ROSA DO TOCANTINS</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DG-RD-PO 00265/2026 · DG-RD-PO 00364/2026</t>
+          <t>DG-RD-PO 00073/2026 · DG-RD-PO 00167/2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20264182405336 · 20264347916892</t>
+          <t>20264088317207 · 20264117832489</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5525,28 +5544,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5750041058</t>
+          <t>5733283256</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SANTA FE DO ARAGUAIA</t>
+          <t>MATEIROS</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00455/2026 · ETO-RD-AR 00752/2026</t>
+          <t>DG-RD-PO 00265/2026 · DG-RD-PO 00364/2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20264172385902 · 20264339038855</t>
+          <t>20264182405336 · 20264347916892</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5563,33 +5582,33 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5700002210</t>
+          <t>5750041058</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TOCANTINOPOLIS</t>
+          <t>SANTA FE DO ARAGUAIA</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00069/2026 · ETO-RD-AG 00339/2026</t>
+          <t>ETO-RD-AR 00455/2026 · ETO-RD-AR 00752/2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20264085517168 · 20264201987012</t>
+          <t>20264172385902 · 20264339038855</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AVARIADO · QUEIMADO</t>
+          <t>QUEIMADO · QUEIMADO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -5601,33 +5620,33 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5700671010</t>
+          <t>5700002210</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LAJEADO</t>
+          <t>TOCANTINOPOLIS</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>121</v>
+        <v>69</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00001/2026 · DOLP-RD-PA 00520/2026</t>
+          <t>ETO-RD-AG 00069/2026 · ETO-RD-AG 00339/2026</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20264062404412 · 20264353620457</t>
+          <t>20264085517168 · 20264201987012</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>QUEIMADO · QUEIMADO</t>
+          <t>AVARIADO · QUEIMADO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -5639,36 +5658,74 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5700036157</t>
+          <t>5700671010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ARAGUANA</t>
+          <t>LAJEADO</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="n">
+        <v>121</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>DOLP-RD-PA 00001/2026 · DOLP-RD-PA 00520/2026</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>20264062404412 · 20264353620457</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>QUEIMADO · QUEIMADO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>5700036157</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ARAGUANA</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
         <v>124</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>ETO-RD-AR 00199/2026 · ETO-RD-AR 00946/2026</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>20264113201352 · 20264477950652</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>AVARIADO · QUEIMADO</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>não</t>
         </is>
@@ -5688,7 +5745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5796,7 +5853,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00605/2026</t>
+          <t>DG-RD-PO 00185/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5816,149 +5873,149 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>O dono martelou queimado assumindo a falta da terceira prova: “leva para queimados só que com pendência de fazer a conferência com o export”. a obra 0112600584 diz “subst. trafo queimado”, a ss e a os dizem queimado, e a crítica casa. o que falta é a extração do material, não a prova — e a etiqueta material não conferido no export fica no caso dizendo isso.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 27 horas da janela; o texto da ss declara falha do equipamento, a crítica registra queimado por descarga atmosferica e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00686/2026</t>
+          <t>DG-RD-PO 00284/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A obra trocou chave fusível</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>o dono pediu categoria própria: “Substituição de chave fusível”. A obra encerrada e conferida não movimentou transformador nenhum — o que ela trocou foi a chave. Estava caindo na categoria genérica de obra sem transformador.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 147 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00587/2026</t>
+          <t>DG-RD-PO 00315/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tape interno</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>o dono mandou excluir na categoria de tape. A observação da própria ocorrência conta o serviço inteiro: “Abertura emergencial do trafo 5700012065 para possibilitar alterar TAP melhoria de tensão. Ao remover a tampa do trafo, caiu dentro do oleo os parafusos. Foi aberto nota e trocado o mesmo.” O transformador foi aberto de propósito para mexer no tape; a troca veio do acidente durante o serviço, não de falha do equipamento. Nenhum texto do caso afirma queima</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 81 horas da janela; o texto da ss declara falha do equipamento, a crítica registra causa nao identificada - especificar e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00468/2026</t>
+          <t>DG-RD-PO 00353/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ausente da base de interrupções</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>o dono reviu a própria decisão: “se estiver fora daquelas janelas … deverão ser excluídos”. Ele havia mandado incluir por ler queima com SIGCO incorreto; conferido na Crítica crua, o código 5301889004 não aparece em papel nenhum nos sete meses — nem com defeito, nem interrompido, nem manobrado. Nem o 5701889004 que a OS escreve, nem o 570188904 que a SS escreve. Sem registro de interrupção não há evento a medir</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 3 horas da janela; o texto da ss declara falha do equipamento, a crítica registra queimado por descarga atmosferica e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00692/2026</t>
+          <t>DOLP-RD-PA 00101/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avaliar com o Matheus</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>o dono mandou tirar do indicador e marcar para avaliar com o Matheus. O caso tem três vozes e elas não fecham: a SS escreve “QUEIMADO AVARIADO” — as duas palavras, na mesma linha —, a obra foi aberta como substituição de trafo avariado, e o custo entrou no projeto SIGCO 8495, que é de avaria. Fica fora da conta enquanto a avaliação não decidir qual das três vale</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 30 horas da janela; o texto da ss declara falha do equipamento, a crítica registra faltando neutro e a obra está fora do export de material.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00739/2026</t>
+          <t>DOLP-RD-PA 00605/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cola e fita — reparo, não troca</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>o dono achou o caso que procurava desde o começo da revisão: “finalmente um caso de cola e fita, exclua ele e classifique como cola e fita”. A OS conta o serviço inteiro — “FEITO COLAGEM E VEDAÇÃO NA BUCHA DO TRAFO 5743290004 QUE ESTAVA COM VAZAMENTO” —, e nenhum transformador foi movimentado: a SS e a OS não trazem série nem tombamento de retirado e instalado. Não houve troca, houve reparo</t>
+          <t>O dono martelou queimado assumindo a falta da terceira prova: “leva para queimados só que com pendência de fazer a conferência com o export”. a obra 0112600584 diz “subst. trafo queimado”, a ss e a os dizem queimado, e a crítica casa. o que falta é a extração do material, não a prova — e a etiqueta material não conferido no export fica no caso dizendo isso.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 01030/2026</t>
+          <t>DOLP-RD-PA 00686/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5968,7 +6025,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tape interno</t>
+          <t>A obra trocou chave fusível</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5978,14 +6035,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>o dono leu o caso e mandou excluir na categoria de tape interno. A OS registra o tape do retirado na posição 05 e o do instalado na 04: a troca moveu o tape, e o tape é interno — não se ajusta em campo. Vale só para este caso: a mesma diferença de posição aparece em 236 das 1.510 e não sustenta regra.</t>
+          <t>o dono pediu categoria própria: “Substituição de chave fusível”. A obra encerrada e conferida não movimentou transformador nenhum — o que ela trocou foi a chave. Estava caindo na categoria genérica de obra sem transformador.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ETO-RD-DP 00156/2026</t>
+          <t>ENC-RD-PS 00317/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6005,14 +6062,14 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>O dono reviu e mandou de volta para a saída como queimado, mantendo a marca: “esse da meta por último também leva para saída de queimado porém coloca essa classificação”. a os diz “transformador substituido pela meta” e a obra está registrada noutra empreiteira — quem executou não é quem o cadastro contratou. isso é etiqueta, não causa: o transformador queimou do mesmo jeito.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 235 horas da janela; o texto da ss declara falha do equipamento, a crítica registra construcao/reforco/extensao de rd e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ETO-RD-DP 00182/2026</t>
+          <t>ETO-RD-AG 00587/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6022,7 +6079,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Furto, roubo ou vandalismo</t>
+          <t>Tape interno</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -6032,14 +6089,14 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>o dono mandou excluir como furto. A SS e a OS são idênticas e explícitas: “Constatado trafo 5700273116 de 15kVA na 19.9kV e para-raios furtados. Acesso bom.” O gatilho de furto já estava aceso e o caso chegava à saída assim mesmo — a codificação da Crítica diz queima, mas a observação dela não descreve sintoma nenhum, e quem esteve no poste escreveu furto</t>
+          <t>o dono mandou excluir na categoria de tape. A observação da própria ocorrência conta o serviço inteiro: “Abertura emergencial do trafo 5700012065 para possibilitar alterar TAP melhoria de tensão. Ao remover a tampa do trafo, caiu dentro do oleo os parafusos. Foi aberto nota e trocado o mesmo.” O transformador foi aberto de propósito para mexer no tape; a troca veio do acidente durante o serviço, não de falha do equipamento. Nenhum texto do caso afirma queima</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00279/2026</t>
+          <t>ETO-RD-AR 00224/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6059,86 +6116,599 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>O dono martelou queimado e mandou marcar o zero: “queimado e classifica com zero clientes interrompidos”. a crítica registra a ocorrência 20264137433112 com defeito no próprio transformador e a ss abrindo dentro do intervalo dela — fato pleno —, mas nenhum cliente foi interrompido, e a obra 0712600198 está fora do export de material. entra pelo campo e pelo texto, com as duas marcas escritas na linha.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 73 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00534/2026</t>
+          <t>ETO-RD-AR 00327/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cola e fita — reparo, não troca</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>o dono mandou mudar para cola e fita, e o campo confirma sem depender de leitura: a base de SS e OS grava DEFEITO = “COLA E FITA” neste caso — preenchido depois da execução, é o que a equipe fechou. A OS diz “REPARO EM TRAFO COM VAZAMENTO DE ÓLEO” e a obra encerrada e conferida não movimentou transformador nenhum. A SS pediu substituição com aumento de potência; o que se fez foi reparo</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 2194 horas da janela; o texto da ss declara falha do equipamento, a crítica registra animal/passaro na rede e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ETO-RD-GU 00179/2026</t>
+          <t>ETO-RD-AR 00408/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Furto, roubo ou vandalismo</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>o dono mandou excluir como furto, confirmando o que quatro registros independentes de campo já diziam: o SIGCO da obra é 61993 “FURTO DE BENS TRAFO”, a SS traz Origem e Defeito gravados como FURTADO, a Crítica registra observação “transformador furtado” com ZERO cliente interrompido nos dois passos, e o texto da SS diz “transformador e medidor furtado”. A subcausa “queimado por descarga atmosférica” é codificação genérica do despachante, e não descreve o que a equipe achou</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 163 horas da janela; o texto da ss declara falha do equipamento, a crítica registra causa nao identificada - especificar e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>ETO-RD-AR 00436/2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 12 horas da janela; o texto da ss declara falha do equipamento, a crítica registra queimado por causa nao identificada e a obra movimentou 1 transformador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ETO-RD-AR 00468/2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>EXCLUIR</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ausente da base de interrupções</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EXCLUÍDA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>o dono reviu a própria decisão: “se estiver fora daquelas janelas … deverão ser excluídos”. Ele havia mandado incluir por ler queima com SIGCO incorreto; conferido na Crítica crua, o código 5301889004 não aparece em papel nenhum nos sete meses — nem com defeito, nem interrompido, nem manobrado. Nem o 5701889004 que a OS escreve, nem o 570188904 que a SS escreve. Sem registro de interrupção não há evento a medir</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ETO-RD-AR 00604/2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 2 horas da janela; o texto da ss declara falha do equipamento, a crítica registra falha bucha de bt e a obra movimentou 1 transformador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ETO-RD-AR 00692/2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>EXCLUIR</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Avaliar com o Matheus</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EXCLUÍDA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>o dono mandou tirar do indicador e marcar para avaliar com o Matheus. O caso tem três vozes e elas não fecham: a SS escreve “QUEIMADO AVARIADO” — as duas palavras, na mesma linha —, a obra foi aberta como substituição de trafo avariado, e o custo entrou no projeto SIGCO 8495, que é de avaria. Fica fora da conta enquanto a avaliação não decidir qual das três vale</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ETO-RD-AR 00739/2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>EXCLUIR</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Cola e fita — reparo, não troca</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EXCLUÍDA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>o dono achou o caso que procurava desde o começo da revisão: “finalmente um caso de cola e fita, exclua ele e classifique como cola e fita”. A OS conta o serviço inteiro — “FEITO COLAGEM E VEDAÇÃO NA BUCHA DO TRAFO 5743290004 QUE ESTAVA COM VAZAMENTO” —, e nenhum transformador foi movimentado: a SS e a OS não trazem série nem tombamento de retirado e instalado. Não houve troca, houve reparo</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ETO-RD-AR 00740/2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1073 horas da janela; o texto da ss declara falha do equipamento, a crítica registra elo subdimensionado e a obra movimentou 1 transformador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ETO-RD-AR 01030/2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>EXCLUIR</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Tape interno</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EXCLUÍDA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>o dono leu o caso e mandou excluir na categoria de tape interno. A OS registra o tape do retirado na posição 05 e o do instalado na 04: a troca moveu o tape, e o tape é interno — não se ajusta em campo. Vale só para este caso: a mesma diferença de posição aparece em 236 das 1.510 e não sustenta regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ETO-RD-DP 00115/2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1437 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ETO-RD-DP 00156/2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>O dono reviu e mandou de volta para a saída como queimado, mantendo a marca: “esse da meta por último também leva para saída de queimado porém coloca essa classificação”. a os diz “transformador substituido pela meta” e a obra está registrada noutra empreiteira — quem executou não é quem o cadastro contratou. isso é etiqueta, não causa: o transformador queimou do mesmo jeito.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ETO-RD-DP 00182/2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>EXCLUIR</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Furto, roubo ou vandalismo</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EXCLUÍDA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>o dono mandou excluir como furto. A SS e a OS são idênticas e explícitas: “Constatado trafo 5700273116 de 15kVA na 19.9kV e para-raios furtados. Acesso bom.” O gatilho de furto já estava aceso e o caso chegava à saída assim mesmo — a codificação da Crítica diz queima, mas a observação dela não descreve sintoma nenhum, e quem esteve no poste escreveu furto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00199/2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1165 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00208/2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1102 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00279/2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>O dono martelou queimado e mandou marcar o zero: “queimado e classifica com zero clientes interrompidos”. a crítica registra a ocorrência 20264137433112 com defeito no próprio transformador e a ss abrindo dentro do intervalo dela — fato pleno —, mas nenhum cliente foi interrompido, e a obra 0712600198 está fora do export de material. entra pelo campo e pelo texto, com as duas marcas escritas na linha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00405/2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 5 horas da janela; o texto da ss declara falha do equipamento, a crítica registra falha bucha de bt e a obra movimentou 1 transformador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00534/2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>EXCLUIR</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Cola e fita — reparo, não troca</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>EXCLUÍDA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>o dono mandou mudar para cola e fita, e o campo confirma sem depender de leitura: a base de SS e OS grava DEFEITO = “COLA E FITA” neste caso — preenchido depois da execução, é o que a equipe fechou. A OS diz “REPARO EM TRAFO COM VAZAMENTO DE ÓLEO” e a obra encerrada e conferida não movimentou transformador nenhum. A SS pediu substituição com aumento de potência; o que se fez foi reparo</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ETO-RD-GU 00058/2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 19 horas da janela; o texto da ss declara falha do equipamento, a crítica registra rd de at e a obra movimentou 1 transformador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ETO-RD-GU 00061/2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 2561 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ETO-RD-GU 00179/2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>EXCLUIR</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Furto, roubo ou vandalismo</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>EXCLUÍDA</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>o dono mandou excluir como furto, confirmando o que quatro registros independentes de campo já diziam: o SIGCO da obra é 61993 “FURTO DE BENS TRAFO”, a SS traz Origem e Defeito gravados como FURTADO, a Crítica registra observação “transformador furtado” com ZERO cliente interrompido nos dois passos, e o texto da SS diz “transformador e medidor furtado”. A subcausa “queimado por descarga atmosférica” é codificação genérica do despachante, e não descreve o que a equipe achou</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ETO-RD-GU 00305/2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 243 horas da janela; o texto da ss declara falha do equipamento, a crítica registra partido na fase e a obra movimentou 1 transformador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>ETO-RD-GU 00685/2026</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>EXCLUIR</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Abalroamento</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>EXCLUÍDA</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>o dono mandou mover para abalroamento, e as quatro vozes concordam com ele: a Crítica registra causa POSTE DE AT e subcausa ABALROADO, o TMAE repete as duas, a SS foi gravada como ABALROAMENTO e a obra 0412600528 entra no SIGCO 20497 — DANOS CAUSADOS POR TERCEIROS. O caso saía como obra de poste por segurança, que é outra coisa: segurança é a companhia decidindo trocar um poste, abalroamento é um terceiro derrubando. A diferença muda para onde o custo vai — ressarcimento, não manutenção</t>
         </is>

--- a/auditoria-transformadores-134/public/bases/Base_Funis.xlsx
+++ b/auditoria-transformadores-134/public/bases/Base_Funis.xlsx
@@ -526,10 +526,10 @@
         <v>1510</v>
       </c>
       <c r="D5" t="n">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E5" t="n">
-        <v>1289</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="6">
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1289</v>
+        <v>1302</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1289</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="7">
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1289</v>
+        <v>1302</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1289</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="8">
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1289</v>
+        <v>1302</v>
       </c>
       <c r="D8" t="n">
         <v>21</v>
       </c>
       <c r="E8" t="n">
-        <v>1268</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="9">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1268</v>
+        <v>1281</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1268</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="10">
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1268</v>
+        <v>1281</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1268</v>
+        <v>1281</v>
       </c>
     </row>
   </sheetData>
@@ -651,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E139"/>
+  <dimension ref="A1:E140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -709,10 +709,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -728,10 +728,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1047,39 +1047,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GOIANORTE</t>
+          <t>ARAGUATINS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ARAGUATINS</t>
+          <t>GOIANORTE</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>17</v>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -1446,83 +1446,83 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MATEIROS</t>
+          <t>COUTO MAGALHAES</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BREJINHO DE NAZARE</t>
+          <t>MATEIROS</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>10</v>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LAGOA DO TOCANTINS</t>
+          <t>BREJINHO DE NAZARE</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>10</v>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TAGUATINGA</t>
+          <t>LAGOA DO TOCANTINS</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>10</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SILVANOPOLIS</t>
+          <t>TAGUATINGA</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1532,29 +1532,29 @@
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>COUTO MAGALHAES</t>
+          <t>SILVANOPOLIS</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>10</v>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49">
@@ -1636,7 +1636,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ITAPORA DO TOCANTINS</t>
+          <t>CASEARA</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1655,7 +1655,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LIZARDA</t>
+          <t>ITAPORA DO TOCANTINS</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1674,96 +1674,96 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PARAISO DO TOCANTINS</t>
+          <t>LIZARDA</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>9</v>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CRISTALANDIA</t>
+          <t>PARAISO DO TOCANTINS</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>9</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DARCINOPOLIS</t>
+          <t>CRISTALANDIA</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ALIANCA DO TOCANTINS</t>
+          <t>DARCINOPOLIS</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>8</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CASEARA</t>
+          <t>ALIANCA DO TOCANTINS</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>8</v>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60">
@@ -1921,26 +1921,26 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TUPIRATINS</t>
+          <t>PRESIDENTE KENNEDY</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>7</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>RECURSOLANDIA</t>
+          <t>TUPIRATINS</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1950,54 +1950,54 @@
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ITAPIRATINS</t>
+          <t>RECURSOLANDIA</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>7</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PALMEIROPOLIS</t>
+          <t>CHAPADA DE AREIA</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>7</v>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CONCEICAO DO TOCANTINS</t>
+          <t>ITAPIRATINS</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -2016,45 +2016,45 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FILADELFIA</t>
+          <t>AUGUSTINOPOLIS</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>7</v>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t>PALMEIROPOLIS</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>7</v>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FIGUEIROPOLIS</t>
+          <t>CONCEICAO DO TOCANTINS</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -2073,55 +2073,55 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PONTE ALTA DO BOM JESUS</t>
+          <t>FILADELFIA</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PRESIDENTE KENNEDY</t>
+          <t>FATIMA</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TALISMA</t>
+          <t>FIGUEIROPOLIS</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
         <v>7</v>
@@ -2130,7 +2130,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CHAPADA DE AREIA</t>
+          <t>PONTE ALTA DO BOM JESUS</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2149,20 +2149,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AUGUSTINOPOLIS</t>
+          <t>TALISMA</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>6</v>
       </c>
       <c r="C80" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81">
@@ -2263,45 +2263,45 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CENTENARIO</t>
+          <t>SAMPAIO</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>5</v>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ANGICO</t>
+          <t>CENTENARIO</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>5</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CRIXÁS DO TOCANTINS</t>
+          <t>ANGICO</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -2320,45 +2320,45 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DIANOPOLIS</t>
+          <t>COLINAS DO TOCANTINS</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>5</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>NOVA ROSALANDIA</t>
+          <t>CRIXÁS DO TOCANTINS</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>5</v>
       </c>
       <c r="C90" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BANDEIRANTES DO TOCANTINS</t>
+          <t>DIANOPOLIS</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -2377,83 +2377,83 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PIRAQUE</t>
+          <t>NOVA ROSALANDIA</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>5</v>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CARIRI DO TOCANTINS</t>
+          <t>BANDEIRANTES DO TOCANTINS</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>5</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BARRA DO OURO</t>
+          <t>PIRAQUE</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>5</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ARAPOEMA</t>
+          <t>CARIRI DO TOCANTINS</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>5</v>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PEDRO AFONSO</t>
+          <t>BARRA DO OURO</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -2463,124 +2463,124 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ALVORADA</t>
+          <t>ARAPOEMA</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>5</v>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SAO FELIX DO TOCANTINS</t>
+          <t>PEDRO AFONSO</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SUCUPIRA</t>
+          <t>ALVORADA</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SAMPAIO</t>
+          <t>SAO FELIX DO TOCANTINS</t>
         </is>
       </c>
       <c r="B100" t="n">
         <v>4</v>
       </c>
       <c r="C100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>JUARINA</t>
+          <t>SUCUPIRA</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>4</v>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>COLINAS DO TOCANTINS</t>
+          <t>JUARINA</t>
         </is>
       </c>
       <c r="B102" t="n">
         <v>4</v>
       </c>
       <c r="C102" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
@@ -2814,26 +2814,26 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AXIXA DO TOCANTINS</t>
+          <t>BRASILANDIA DO TOCANTINS</t>
         </is>
       </c>
       <c r="B115" t="n">
         <v>3</v>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>PRAIA NORTE</t>
+          <t>AXIXA DO TOCANTINS</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -2852,26 +2852,26 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BARROLANDIA</t>
+          <t>PRAIA NORTE</t>
         </is>
       </c>
       <c r="B117" t="n">
         <v>3</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE DO TOCANTINS</t>
+          <t>BARROLANDIA</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -2890,49 +2890,49 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ITAGUATINS</t>
+          <t>PORTO ALEGRE DO TOCANTINS</t>
         </is>
       </c>
       <c r="B119" t="n">
         <v>3</v>
       </c>
       <c r="C119" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" t="n">
         <v>3</v>
-      </c>
-      <c r="D119" t="n">
-        <v>0</v>
-      </c>
-      <c r="E119" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ABREULANDIA</t>
+          <t>ITAGUATINS</t>
         </is>
       </c>
       <c r="B120" t="n">
         <v>3</v>
       </c>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>RIACHINHO</t>
+          <t>ABREULANDIA</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -2941,13 +2941,13 @@
         <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RIO DOS BOIS</t>
+          <t>RIACHINHO</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -2966,26 +2966,26 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>NAZARE</t>
+          <t>RIO DOS BOIS</t>
         </is>
       </c>
       <c r="B123" t="n">
         <v>2</v>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SANTA TEREZINHA DO TOCANTINS</t>
+          <t>NAZARE</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -3004,7 +3004,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PUGMIL</t>
+          <t>SANTA TEREZINHA DO TOCANTINS</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -3023,7 +3023,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BRASILANDIA DO TOCANTINS</t>
+          <t>PUGMIL</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -3099,26 +3099,26 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CARRASCO BONITO</t>
+          <t>NOVO PLANALTO</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>1</v>
       </c>
       <c r="C130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
       </c>
       <c r="E130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>RIO DA CONCEICAO</t>
+          <t>CARRASCO BONITO</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -3137,7 +3137,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SAO SEBASTIAO DO TOCANTINS</t>
+          <t>RIO DA CONCEICAO</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -3156,64 +3156,64 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>FORTALEZA DO TABOCAO</t>
+          <t>SAO SEBASTIAO DO TOCANTINS</t>
         </is>
       </c>
       <c r="B133" t="n">
         <v>1</v>
       </c>
       <c r="C133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>COMBINADO</t>
+          <t>FORTALEZA DO TABOCAO</t>
         </is>
       </c>
       <c r="B134" t="n">
         <v>1</v>
       </c>
       <c r="C134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
       </c>
       <c r="E134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>NOVO ALEGRE</t>
+          <t>COMBINADO</t>
         </is>
       </c>
       <c r="B135" t="n">
         <v>1</v>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
       </c>
       <c r="E135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CARMOLANDIA</t>
+          <t>NOVO ALEGRE</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -3232,7 +3232,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MAURILANDIA DO TOCANTINS</t>
+          <t>CARMOLANDIA</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -3251,7 +3251,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AURORA DO TOCANTINS</t>
+          <t>MAURILANDIA DO TOCANTINS</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -3270,19 +3270,38 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>AURORA DO TOCANTINS</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
           <t>ANANAS</t>
         </is>
       </c>
-      <c r="B139" t="n">
-        <v>1</v>
-      </c>
-      <c r="C139" t="n">
-        <v>1</v>
-      </c>
-      <c r="D139" t="n">
-        <v>0</v>
-      </c>
-      <c r="E139" t="n">
+      <c r="B140" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3344,11 +3363,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>79.9%</t>
         </is>
       </c>
     </row>
@@ -3359,11 +3378,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.9%</t>
         </is>
       </c>
     </row>
@@ -3374,11 +3393,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1268</v>
+        <v>1281</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>84.8%</t>
         </is>
       </c>
     </row>
@@ -3389,11 +3408,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>13.8%</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3473,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>221 exclusões em 23 categorias, e elas se dividem em duas famílias que convém não misturar: 118 não têm interrupção que sustente o caso e 103 têm causa ou documento fora do indicador.</t>
+          <t>208 exclusões em 23 categorias, e elas se dividem em duas famílias que convém não misturar: 105 não têm interrupção que sustente o caso e 103 têm causa ou documento fora do indicador.</t>
         </is>
       </c>
     </row>
@@ -3508,7 +3527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3529,11 +3548,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3558,7 +3577,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3583,7 +3602,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3608,7 +3627,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3633,7 +3652,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3658,7 +3677,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3683,7 +3702,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3708,7 +3727,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3733,7 +3752,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3758,7 +3777,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3783,7 +3802,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3808,7 +3827,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3833,7 +3852,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3858,7 +3877,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4140,7 +4159,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -4170,7 +4189,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -4252,7 +4271,7 @@
         <v>123</v>
       </c>
       <c r="C5" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -5745,7 +5764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5880,7 +5899,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DG-RD-PO 00284/2026</t>
+          <t>DG-RD-PO 00209/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5890,7 +5909,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>AVARIADO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -5900,14 +5919,14 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 147 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra queimado por descarga atmosferica e a obra movimentou 1 transformador. saía do indicador por estar a 15 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DG-RD-PO 00315/2026</t>
+          <t>DG-RD-PO 00284/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5927,14 +5946,14 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 81 horas da janela; o texto da ss declara falha do equipamento, a crítica registra causa nao identificada - especificar e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 147 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DG-RD-PO 00353/2026</t>
+          <t>DG-RD-PO 00315/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5954,14 +5973,14 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 3 horas da janela; o texto da ss declara falha do equipamento, a crítica registra queimado por descarga atmosferica e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 81 horas da janela; o texto da ss declara falha do equipamento, a crítica registra causa nao identificada - especificar e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00101/2026</t>
+          <t>DG-RD-PO 00353/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5981,14 +6000,14 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 30 horas da janela; o texto da ss declara falha do equipamento, a crítica registra faltando neutro e a obra está fora do export de material.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 3 horas da janela; o texto da ss declara falha do equipamento, a crítica registra queimado por descarga atmosferica e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00605/2026</t>
+          <t>DOLP-RD-PA 00101/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6008,41 +6027,41 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>O dono martelou queimado assumindo a falta da terceira prova: “leva para queimados só que com pendência de fazer a conferência com o export”. a obra 0112600584 diz “subst. trafo queimado”, a ss e a os dizem queimado, e a crítica casa. o que falta é a extração do material, não a prova — e a etiqueta material não conferido no export fica no caso dizendo isso.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 30 horas da janela; o texto da ss declara falha do equipamento, a crítica registra faltando neutro e a obra está fora do export de material.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00686/2026</t>
+          <t>DOLP-RD-PA 00458/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A obra trocou chave fusível</t>
+          <t>AVARIADO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>o dono pediu categoria própria: “Substituição de chave fusível”. A obra encerrada e conferida não movimentou transformador nenhum — o que ela trocou foi a chave. Estava caindo na categoria genérica de obra sem transformador.</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra vazamento de oleo / tanque deteriorado e a obra movimentou 1 transformador. saía do indicador por estar a 2 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00317/2026</t>
+          <t>DOLP-RD-PA 00521/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6052,7 +6071,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>AVARIADO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -6062,68 +6081,68 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 235 horas da janela; o texto da ss declara falha do equipamento, a crítica registra construcao/reforco/extensao de rd e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra vazamento de oleo / tanque deteriorado e a obra movimentou 1 transformador. saía do indicador por estar a 3 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00587/2026</t>
+          <t>DOLP-RD-PA 00605/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tape interno</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>o dono mandou excluir na categoria de tape. A observação da própria ocorrência conta o serviço inteiro: “Abertura emergencial do trafo 5700012065 para possibilitar alterar TAP melhoria de tensão. Ao remover a tampa do trafo, caiu dentro do oleo os parafusos. Foi aberto nota e trocado o mesmo.” O transformador foi aberto de propósito para mexer no tape; a troca veio do acidente durante o serviço, não de falha do equipamento. Nenhum texto do caso afirma queima</t>
+          <t>O dono martelou queimado assumindo a falta da terceira prova: “leva para queimados só que com pendência de fazer a conferência com o export”. a obra 0112600584 diz “subst. trafo queimado”, a ss e a os dizem queimado, e a crítica casa. o que falta é a extração do material, não a prova — e a etiqueta material não conferido no export fica no caso dizendo isso.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00224/2026</t>
+          <t>DOLP-RD-PA 00686/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>A obra trocou chave fusível</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 73 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+          <t>o dono pediu categoria própria: “Substituição de chave fusível”. A obra encerrada e conferida não movimentou transformador nenhum — o que ela trocou foi a chave. Estava caindo na categoria genérica de obra sem transformador.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00327/2026</t>
+          <t>ENC-RD-PS 00116/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6143,14 +6162,14 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 2194 horas da janela; o texto da ss declara falha do equipamento, a crítica registra animal/passaro na rede e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara queimado; a crítica registra causa nao identificada - especificar e a obra movimentou 1 transformador. saía do indicador por estar a 3801 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00408/2026</t>
+          <t>ENC-RD-PS 00317/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6170,14 +6189,14 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 163 horas da janela; o texto da ss declara falha do equipamento, a crítica registra causa nao identificada - especificar e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 235 horas da janela; o texto da ss declara falha do equipamento, a crítica registra construcao/reforco/extensao de rd e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00436/2026</t>
+          <t>ENC-RD-PS 00487/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6187,7 +6206,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>AVARIADO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -6197,41 +6216,41 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 12 horas da janela; o texto da ss declara falha do equipamento, a crítica registra queimado por causa nao identificada e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra queimado por sobrecarga e a obra movimentou 1 transformador. saía do indicador por estar a 28 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00468/2026</t>
+          <t>ETO-RD-AG 00117/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ausente da base de interrupções</t>
+          <t>AVARIADO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>o dono reviu a própria decisão: “se estiver fora daquelas janelas … deverão ser excluídos”. Ele havia mandado incluir por ler queima com SIGCO incorreto; conferido na Crítica crua, o código 5301889004 não aparece em papel nenhum nos sete meses — nem com defeito, nem interrompido, nem manobrado. Nem o 5701889004 que a OS escreve, nem o 570188904 que a SS escreve. Sem registro de interrupção não há evento a medir</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra arvore de pequeno/ medio porte na rede / na faixa e a obra movimentou 1 transformador. saía do indicador por estar a 691 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00604/2026</t>
+          <t>ETO-RD-AG 00327/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6241,7 +6260,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>AVARIADO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -6251,122 +6270,122 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 2 horas da janela; o texto da ss declara falha do equipamento, a crítica registra falha bucha de bt e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra vazamento de oleo / tanque deteriorado e a obra movimentou 1 transformador. saía do indicador por estar a 5 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00692/2026</t>
+          <t>ETO-RD-AG 00493/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avaliar com o Matheus</t>
+          <t>AVARIADO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>o dono mandou tirar do indicador e marcar para avaliar com o Matheus. O caso tem três vozes e elas não fecham: a SS escreve “QUEIMADO AVARIADO” — as duas palavras, na mesma linha —, a obra foi aberta como substituição de trafo avariado, e o custo entrou no projeto SIGCO 8495, que é de avaria. Fica fora da conta enquanto a avaliação não decidir qual das três vale</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra rd de at e a obra movimentou 1 transformador. saía do indicador por estar a 4 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00739/2026</t>
+          <t>ETO-RD-AG 00501/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cola e fita — reparo, não troca</t>
+          <t>AVARIADO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>o dono achou o caso que procurava desde o começo da revisão: “finalmente um caso de cola e fita, exclua ele e classifique como cola e fita”. A OS conta o serviço inteiro — “FEITO COLAGEM E VEDAÇÃO NA BUCHA DO TRAFO 5743290004 QUE ESTAVA COM VAZAMENTO” —, e nenhum transformador foi movimentado: a SS e a OS não trazem série nem tombamento de retirado e instalado. Não houve troca, houve reparo</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra vazamento de oleo / tanque deteriorado e a obra movimentou 1 transformador. saía do indicador por estar a 3 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00740/2026</t>
+          <t>ETO-RD-AG 00587/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>Tape interno</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1073 horas da janela; o texto da ss declara falha do equipamento, a crítica registra elo subdimensionado e a obra movimentou 1 transformador.</t>
+          <t>o dono mandou excluir na categoria de tape. A observação da própria ocorrência conta o serviço inteiro: “Abertura emergencial do trafo 5700012065 para possibilitar alterar TAP melhoria de tensão. Ao remover a tampa do trafo, caiu dentro do oleo os parafusos. Foi aberto nota e trocado o mesmo.” O transformador foi aberto de propósito para mexer no tape; a troca veio do acidente durante o serviço, não de falha do equipamento. Nenhum texto do caso afirma queima</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 01030/2026</t>
+          <t>ETO-RD-AR 00224/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tape interno</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>o dono leu o caso e mandou excluir na categoria de tape interno. A OS registra o tape do retirado na posição 05 e o do instalado na 04: a troca moveu o tape, e o tape é interno — não se ajusta em campo. Vale só para este caso: a mesma diferença de posição aparece em 236 das 1.510 e não sustenta regra.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 73 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ETO-RD-DP 00115/2026</t>
+          <t>ETO-RD-AR 00327/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6386,14 +6405,14 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1437 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 2194 horas da janela; o texto da ss declara falha do equipamento, a crítica registra animal/passaro na rede e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ETO-RD-DP 00156/2026</t>
+          <t>ETO-RD-AR 00408/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6413,68 +6432,68 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>O dono reviu e mandou de volta para a saída como queimado, mantendo a marca: “esse da meta por último também leva para saída de queimado porém coloca essa classificação”. a os diz “transformador substituido pela meta” e a obra está registrada noutra empreiteira — quem executou não é quem o cadastro contratou. isso é etiqueta, não causa: o transformador queimou do mesmo jeito.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 163 horas da janela; o texto da ss declara falha do equipamento, a crítica registra causa nao identificada - especificar e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ETO-RD-DP 00182/2026</t>
+          <t>ETO-RD-AR 00436/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Furto, roubo ou vandalismo</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>o dono mandou excluir como furto. A SS e a OS são idênticas e explícitas: “Constatado trafo 5700273116 de 15kVA na 19.9kV e para-raios furtados. Acesso bom.” O gatilho de furto já estava aceso e o caso chegava à saída assim mesmo — a codificação da Crítica diz queima, mas a observação dela não descreve sintoma nenhum, e quem esteve no poste escreveu furto</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 12 horas da janela; o texto da ss declara falha do equipamento, a crítica registra queimado por causa nao identificada e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00199/2026</t>
+          <t>ETO-RD-AR 00468/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>Ausente da base de interrupções</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1165 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+          <t>o dono reviu a própria decisão: “se estiver fora daquelas janelas … deverão ser excluídos”. Ele havia mandado incluir por ler queima com SIGCO incorreto; conferido na Crítica crua, o código 5301889004 não aparece em papel nenhum nos sete meses — nem com defeito, nem interrompido, nem manobrado. Nem o 5701889004 que a OS escreve, nem o 570188904 que a SS escreve. Sem registro de interrupção não há evento a medir</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00208/2026</t>
+          <t>ETO-RD-AR 00604/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6494,122 +6513,122 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1102 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 2 horas da janela; o texto da ss declara falha do equipamento, a crítica registra falha bucha de bt e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00279/2026</t>
+          <t>ETO-RD-AR 00692/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>Avaliar com o Matheus</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>O dono martelou queimado e mandou marcar o zero: “queimado e classifica com zero clientes interrompidos”. a crítica registra a ocorrência 20264137433112 com defeito no próprio transformador e a ss abrindo dentro do intervalo dela — fato pleno —, mas nenhum cliente foi interrompido, e a obra 0712600198 está fora do export de material. entra pelo campo e pelo texto, com as duas marcas escritas na linha.</t>
+          <t>o dono mandou tirar do indicador e marcar para avaliar com o Matheus. O caso tem três vozes e elas não fecham: a SS escreve “QUEIMADO AVARIADO” — as duas palavras, na mesma linha —, a obra foi aberta como substituição de trafo avariado, e o custo entrou no projeto SIGCO 8495, que é de avaria. Fica fora da conta enquanto a avaliação não decidir qual das três vale</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00405/2026</t>
+          <t>ETO-RD-AR 00739/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>Cola e fita — reparo, não troca</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 5 horas da janela; o texto da ss declara falha do equipamento, a crítica registra falha bucha de bt e a obra movimentou 1 transformador.</t>
+          <t>o dono achou o caso que procurava desde o começo da revisão: “finalmente um caso de cola e fita, exclua ele e classifique como cola e fita”. A OS conta o serviço inteiro — “FEITO COLAGEM E VEDAÇÃO NA BUCHA DO TRAFO 5743290004 QUE ESTAVA COM VAZAMENTO” —, e nenhum transformador foi movimentado: a SS e a OS não trazem série nem tombamento de retirado e instalado. Não houve troca, houve reparo</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00534/2026</t>
+          <t>ETO-RD-AR 00740/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cola e fita — reparo, não troca</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>o dono mandou mudar para cola e fita, e o campo confirma sem depender de leitura: a base de SS e OS grava DEFEITO = “COLA E FITA” neste caso — preenchido depois da execução, é o que a equipe fechou. A OS diz “REPARO EM TRAFO COM VAZAMENTO DE ÓLEO” e a obra encerrada e conferida não movimentou transformador nenhum. A SS pediu substituição com aumento de potência; o que se fez foi reparo</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1073 horas da janela; o texto da ss declara falha do equipamento, a crítica registra elo subdimensionado e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ETO-RD-GU 00058/2026</t>
+          <t>ETO-RD-AR 01030/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>Tape interno</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 19 horas da janela; o texto da ss declara falha do equipamento, a crítica registra rd de at e a obra movimentou 1 transformador.</t>
+          <t>o dono leu o caso e mandou excluir na categoria de tape interno. A OS registra o tape do retirado na posição 05 e o do instalado na 04: a troca moveu o tape, e o tape é interno — não se ajusta em campo. Vale só para este caso: a mesma diferença de posição aparece em 236 das 1.510 e não sustenta regra.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ETO-RD-GU 00061/2026</t>
+          <t>ETO-RD-DP 00115/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6629,86 +6648,437 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 2561 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1437 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ETO-RD-GU 00179/2026</t>
+          <t>ETO-RD-DP 00156/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Furto, roubo ou vandalismo</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>o dono mandou excluir como furto, confirmando o que quatro registros independentes de campo já diziam: o SIGCO da obra é 61993 “FURTO DE BENS TRAFO”, a SS traz Origem e Defeito gravados como FURTADO, a Crítica registra observação “transformador furtado” com ZERO cliente interrompido nos dois passos, e o texto da SS diz “transformador e medidor furtado”. A subcausa “queimado por descarga atmosférica” é codificação genérica do despachante, e não descreve o que a equipe achou</t>
+          <t>O dono reviu e mandou de volta para a saída como queimado, mantendo a marca: “esse da meta por último também leva para saída de queimado porém coloca essa classificação”. a os diz “transformador substituido pela meta” e a obra está registrada noutra empreiteira — quem executou não é quem o cadastro contratou. isso é etiqueta, não causa: o transformador queimou do mesmo jeito.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ETO-RD-GU 00305/2026</t>
+          <t>ETO-RD-DP 00182/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>Furto, roubo ou vandalismo</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 243 horas da janela; o texto da ss declara falha do equipamento, a crítica registra partido na fase e a obra movimentou 1 transformador.</t>
+          <t>o dono mandou excluir como furto. A SS e a OS são idênticas e explícitas: “Constatado trafo 5700273116 de 15kVA na 19.9kV e para-raios furtados. Acesso bom.” O gatilho de furto já estava aceso e o caso chegava à saída assim mesmo — a codificação da Crítica diz queima, mas a observação dela não descreve sintoma nenhum, e quem esteve no poste escreveu furto</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>ETO-RD-GR 00167/2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara queimado; a crítica registra descarga atmosferica e a obra movimentou 1 transformador. saía do indicador por estar a 24 horas da janela.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00199/2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1165 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00208/2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1102 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00278/2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AVARIADO</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra descarga atmosferica e a obra movimentou 1 transformador. saía do indicador por estar a 142 horas da janela.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00279/2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>O dono martelou queimado e mandou marcar o zero: “queimado e classifica com zero clientes interrompidos”. a crítica registra a ocorrência 20264137433112 com defeito no próprio transformador e a ss abrindo dentro do intervalo dela — fato pleno —, mas nenhum cliente foi interrompido, e a obra 0712600198 está fora do export de material. entra pelo campo e pelo texto, com as duas marcas escritas na linha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00324/2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AVARIADO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra vazamento de oleo / tanque deteriorado e a obra movimentou 1 transformador. saía do indicador por estar a 15 horas da janela.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00373/2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AVARIADO</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra descarga atmosferica e a obra movimentou 1 transformador. saía do indicador por estar a 166 horas da janela.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00405/2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 5 horas da janela; o texto da ss declara falha do equipamento, a crítica registra falha bucha de bt e a obra movimentou 1 transformador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00534/2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>EXCLUIR</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Cola e fita — reparo, não troca</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>EXCLUÍDA</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>o dono mandou mudar para cola e fita, e o campo confirma sem depender de leitura: a base de SS e OS grava DEFEITO = “COLA E FITA” neste caso — preenchido depois da execução, é o que a equipe fechou. A OS diz “REPARO EM TRAFO COM VAZAMENTO DE ÓLEO” e a obra encerrada e conferida não movimentou transformador nenhum. A SS pediu substituição com aumento de potência; o que se fez foi reparo</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ETO-RD-GU 00058/2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 19 horas da janela; o texto da ss declara falha do equipamento, a crítica registra rd de at e a obra movimentou 1 transformador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ETO-RD-GU 00061/2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 2561 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ETO-RD-GU 00179/2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>EXCLUIR</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Furto, roubo ou vandalismo</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>EXCLUÍDA</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>o dono mandou excluir como furto, confirmando o que quatro registros independentes de campo já diziam: o SIGCO da obra é 61993 “FURTO DE BENS TRAFO”, a SS traz Origem e Defeito gravados como FURTADO, a Crítica registra observação “transformador furtado” com ZERO cliente interrompido nos dois passos, e o texto da SS diz “transformador e medidor furtado”. A subcausa “queimado por descarga atmosférica” é codificação genérica do despachante, e não descreve o que a equipe achou</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ETO-RD-GU 00305/2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 243 horas da janela; o texto da ss declara falha do equipamento, a crítica registra partido na fase e a obra movimentou 1 transformador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>ETO-RD-GU 00685/2026</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>EXCLUIR</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Abalroamento</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>EXCLUÍDA</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>o dono mandou mover para abalroamento, e as quatro vozes concordam com ele: a Crítica registra causa POSTE DE AT e subcausa ABALROADO, o TMAE repete as duas, a SS foi gravada como ABALROAMENTO e a obra 0412600528 entra no SIGCO 20497 — DANOS CAUSADOS POR TERCEIROS. O caso saía como obra de poste por segurança, que é outra coisa: segurança é a companhia decidindo trocar um poste, abalroamento é um terceiro derrubando. A diferença muda para onde o custo vai — ressarcimento, não manutenção</t>
         </is>

--- a/auditoria-transformadores-134/public/bases/Base_Funis.xlsx
+++ b/auditoria-transformadores-134/public/bases/Base_Funis.xlsx
@@ -526,10 +526,10 @@
         <v>1510</v>
       </c>
       <c r="D5" t="n">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="E5" t="n">
-        <v>1302</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="6">
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1302</v>
+        <v>1294</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1302</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="7">
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1302</v>
+        <v>1294</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1302</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="8">
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1302</v>
+        <v>1294</v>
       </c>
       <c r="D8" t="n">
         <v>21</v>
       </c>
       <c r="E8" t="n">
-        <v>1281</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="9">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1281</v>
+        <v>1273</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1281</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="10">
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1281</v>
+        <v>1273</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1281</v>
+        <v>1273</v>
       </c>
     </row>
   </sheetData>
@@ -709,10 +709,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -1085,26 +1085,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SANTA FE DO ARAGUAIA</t>
+          <t>CHAPADA DA NATIVIDADE</t>
         </is>
       </c>
       <c r="B24" t="n">
+        <v>15</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
         <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>3</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CHAPADA DA NATIVIDADE</t>
+          <t>GURUPI</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1123,58 +1123,58 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GURUPI</t>
+          <t>SANDOLANDIA</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>15</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SANDOLANDIA</t>
+          <t>GUARAI</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>15</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GUARAI</t>
+          <t>SANTA FE DO ARAGUAIA</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>15</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
@@ -1560,45 +1560,45 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BABACULANDIA</t>
+          <t>NATIVIDADE</t>
         </is>
       </c>
       <c r="B49" t="n">
+        <v>9</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
         <v>10</v>
-      </c>
-      <c r="C49" t="n">
-        <v>6</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NATIVIDADE</t>
+          <t>ALMAS</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>9</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ALMAS</t>
+          <t>APARECIDA DO RIO NEGRO</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1608,16 +1608,16 @@
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>APARECIDA DO RIO NEGRO</t>
+          <t>CASEARA</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1636,7 +1636,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CASEARA</t>
+          <t>ITAPORA DO TOCANTINS</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1655,7 +1655,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ITAPORA DO TOCANTINS</t>
+          <t>LIZARDA</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1674,58 +1674,58 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>LIZARDA</t>
+          <t>PARAISO DO TOCANTINS</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>9</v>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PARAISO DO TOCANTINS</t>
+          <t>CRISTALANDIA</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>9</v>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CRISTALANDIA</t>
+          <t>BABACULANDIA</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>9</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58">
@@ -2263,83 +2263,83 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SAMPAIO</t>
+          <t>CENTENARIO</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>5</v>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CENTENARIO</t>
+          <t>ANGICO</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>5</v>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ANGICO</t>
+          <t>COLINAS DO TOCANTINS</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>5</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>COLINAS DO TOCANTINS</t>
+          <t>CRIXÁS DO TOCANTINS</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>5</v>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CRIXÁS DO TOCANTINS</t>
+          <t>DIANOPOLIS</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -2358,102 +2358,102 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DIANOPOLIS</t>
+          <t>NOVA ROSALANDIA</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>5</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>NOVA ROSALANDIA</t>
+          <t>BANDEIRANTES DO TOCANTINS</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>5</v>
       </c>
       <c r="C92" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BANDEIRANTES DO TOCANTINS</t>
+          <t>PIRAQUE</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>5</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PIRAQUE</t>
+          <t>CARIRI DO TOCANTINS</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>5</v>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CARIRI DO TOCANTINS</t>
+          <t>ARAPOEMA</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>5</v>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BARRA DO OURO</t>
+          <t>PEDRO AFONSO</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -2463,111 +2463,111 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ARAPOEMA</t>
+          <t>ALVORADA</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>5</v>
       </c>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PEDRO AFONSO</t>
+          <t>SAO FELIX DO TOCANTINS</t>
         </is>
       </c>
       <c r="B98" t="n">
+        <v>4</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
         <v>5</v>
-      </c>
-      <c r="C98" t="n">
-        <v>0</v>
-      </c>
-      <c r="D98" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ALVORADA</t>
+          <t>SUCUPIRA</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SAO FELIX DO TOCANTINS</t>
+          <t>SAMPAIO</t>
         </is>
       </c>
       <c r="B100" t="n">
         <v>4</v>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SUCUPIRA</t>
+          <t>JUARINA</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>4</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>JUARINA</t>
+          <t>BOM JESUS DO TOCANTINS</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -2586,26 +2586,26 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BOM JESUS DO TOCANTINS</t>
+          <t>TUPIRAMA</t>
         </is>
       </c>
       <c r="B103" t="n">
         <v>4</v>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TUPIRAMA</t>
+          <t>JAU DO TOCANTINS</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -2624,7 +2624,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>JAU DO TOCANTINS</t>
+          <t>SANTA MARIA DO TOCANTINS</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -2643,77 +2643,77 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SANTA MARIA DO TOCANTINS</t>
+          <t>TOCANTINIA</t>
         </is>
       </c>
       <c r="B106" t="n">
         <v>4</v>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>TOCANTINIA</t>
+          <t>OLIVEIRA DE FATIMA</t>
         </is>
       </c>
       <c r="B107" t="n">
         <v>4</v>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>OLIVEIRA DE FATIMA</t>
+          <t>NOVO ACORDO</t>
         </is>
       </c>
       <c r="B108" t="n">
         <v>4</v>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>NOVO ACORDO</t>
+          <t>BARRA DO OURO</t>
         </is>
       </c>
       <c r="B109" t="n">
         <v>4</v>
       </c>
       <c r="C109" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110">
@@ -2966,26 +2966,26 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>RIO DOS BOIS</t>
+          <t>NAZARE</t>
         </is>
       </c>
       <c r="B123" t="n">
         <v>2</v>
       </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>NAZARE</t>
+          <t>SANTA TEREZINHA DO TOCANTINS</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -3004,7 +3004,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SANTA TEREZINHA DO TOCANTINS</t>
+          <t>PUGMIL</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -3023,102 +3023,102 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PUGMIL</t>
+          <t>AGUIARNOPOLIS</t>
         </is>
       </c>
       <c r="B126" t="n">
         <v>2</v>
       </c>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AGUIARNOPOLIS</t>
+          <t>SAO BENTO DO TOCANTINS</t>
         </is>
       </c>
       <c r="B127" t="n">
         <v>2</v>
       </c>
       <c r="C127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SAO BENTO DO TOCANTINS</t>
+          <t>SITIO NOVO DO TOCANTINS</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SITIO NOVO DO TOCANTINS</t>
+          <t>NOVO PLANALTO</t>
         </is>
       </c>
       <c r="B129" t="n">
         <v>1</v>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
       </c>
       <c r="E129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>NOVO PLANALTO</t>
+          <t>CARRASCO BONITO</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>1</v>
       </c>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
       </c>
       <c r="E130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CARRASCO BONITO</t>
+          <t>RIO DA CONCEICAO</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -3137,7 +3137,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>RIO DA CONCEICAO</t>
+          <t>SAO SEBASTIAO DO TOCANTINS</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -3156,64 +3156,64 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SAO SEBASTIAO DO TOCANTINS</t>
+          <t>FORTALEZA DO TABOCAO</t>
         </is>
       </c>
       <c r="B133" t="n">
         <v>1</v>
       </c>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>FORTALEZA DO TABOCAO</t>
+          <t>COMBINADO</t>
         </is>
       </c>
       <c r="B134" t="n">
         <v>1</v>
       </c>
       <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
         <v>2</v>
-      </c>
-      <c r="D134" t="n">
-        <v>0</v>
-      </c>
-      <c r="E134" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>COMBINADO</t>
+          <t>NOVO ALEGRE</t>
         </is>
       </c>
       <c r="B135" t="n">
         <v>1</v>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
       </c>
       <c r="E135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>NOVO ALEGRE</t>
+          <t>CARMOLANDIA</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -3232,20 +3232,20 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CARMOLANDIA</t>
+          <t>RIO DOS BOIS</t>
         </is>
       </c>
       <c r="B137" t="n">
         <v>1</v>
       </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
@@ -3363,11 +3363,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>79.6%</t>
         </is>
       </c>
     </row>
@@ -3378,11 +3378,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>4.7%</t>
         </is>
       </c>
     </row>
@@ -3393,11 +3393,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1281</v>
+        <v>1273</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>84.3%</t>
         </is>
       </c>
     </row>
@@ -3408,11 +3408,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>208 exclusões em 23 categorias, e elas se dividem em duas famílias que convém não misturar: 105 não têm interrupção que sustente o caso e 103 têm causa ou documento fora do indicador.</t>
+          <t>216 exclusões em 23 categorias, e elas se dividem em duas famílias que convém não misturar: 105 não têm interrupção que sustente o caso e 111 têm causa ou documento fora do indicador.</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3614,20 +3614,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Remanejamento</t>
+          <t>Preventivo ou programado</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>remanejamento</t>
+          <t>preventivo</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3639,20 +3639,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tape interno</t>
+          <t>Remanejamento</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>tap</t>
+          <t>remanejamento</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3664,20 +3664,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sem OS e sem obra</t>
+          <t>Tape interno</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sem_os</t>
+          <t>tap</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3689,12 +3689,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Abalroamento</t>
+          <t>Sem OS e sem obra</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>abalroamento</t>
+          <t>sem_os</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3714,20 +3714,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Obra encerrada sem transformador</t>
+          <t>Abalroamento</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>obra_sem_transformador</t>
+          <t>abalroamento</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3739,20 +3739,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Preventivo ou programado</t>
+          <t>Obra encerrada sem transformador</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>preventivo</t>
+          <t>obra_sem_transformador</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4258,7 +4258,7 @@
         <v>1283</v>
       </c>
       <c r="C4" t="n">
-        <v>1212</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="5">
@@ -4271,7 +4271,7 @@
         <v>123</v>
       </c>
       <c r="C5" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6">
@@ -5224,7 +5224,7 @@
         <v>62</v>
       </c>
       <c r="C4" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6034,34 +6034,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00458/2026</t>
+          <t>DOLP-RD-PA 00369/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AVARIADO</t>
+          <t>Preventivo ou programado</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra vazamento de oleo / tanque deteriorado e a obra movimentou 1 transformador. saía do indicador por estar a 2 horas da janela.</t>
+          <t>o dono mandou mover para preventivo: “mova do lugar de onde está e coloca no preventivo”. A SS não foi aberta pelo COI — foi aberta pela própria manutenção, ou seja, a equipe achou o defeito antes de o cliente reclamar. O texto declara queimado e a obra movimentou transformador; o que muda não é o que aconteceu com o equipamento, é o enquadramento: troca encontrada em ronda não é falha que penalizou o indicador</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00521/2026</t>
+          <t>DOLP-RD-PA 00458/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6081,68 +6081,68 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra vazamento de oleo / tanque deteriorado e a obra movimentou 1 transformador. saía do indicador por estar a 3 horas da janela.</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra vazamento de oleo / tanque deteriorado e a obra movimentou 1 transformador. saía do indicador por estar a 2 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00605/2026</t>
+          <t>DOLP-RD-PA 00488/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>Preventivo ou programado</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>O dono martelou queimado assumindo a falta da terceira prova: “leva para queimados só que com pendência de fazer a conferência com o export”. a obra 0112600584 diz “subst. trafo queimado”, a ss e a os dizem queimado, e a crítica casa. o que falta é a extração do material, não a prova — e a etiqueta material não conferido no export fica no caso dizendo isso.</t>
+          <t>o dono mandou mover para preventivo: “mova do lugar de onde está e coloca no preventivo”. A SS não foi aberta pelo COI — foi aberta pelo COCM, ou seja, a equipe achou o defeito antes de o cliente reclamar. O texto declara avariado e a obra movimentou transformador; o que muda não é o que aconteceu com o equipamento, é o enquadramento: troca encontrada em ronda não é falha que penalizou o indicador</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00686/2026</t>
+          <t>DOLP-RD-PA 00521/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A obra trocou chave fusível</t>
+          <t>AVARIADO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>o dono pediu categoria própria: “Substituição de chave fusível”. A obra encerrada e conferida não movimentou transformador nenhum — o que ela trocou foi a chave. Estava caindo na categoria genérica de obra sem transformador.</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra vazamento de oleo / tanque deteriorado e a obra movimentou 1 transformador. saía do indicador por estar a 3 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00116/2026</t>
+          <t>DOLP-RD-PA 00605/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6162,95 +6162,95 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara queimado; a crítica registra causa nao identificada - especificar e a obra movimentou 1 transformador. saía do indicador por estar a 3801 horas da janela.</t>
+          <t>O dono martelou queimado assumindo a falta da terceira prova: “leva para queimados só que com pendência de fazer a conferência com o export”. a obra 0112600584 diz “subst. trafo queimado”, a ss e a os dizem queimado, e a crítica casa. o que falta é a extração do material, não a prova — e a etiqueta material não conferido no export fica no caso dizendo isso.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00317/2026</t>
+          <t>DOLP-RD-PA 00686/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>A obra trocou chave fusível</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 235 horas da janela; o texto da ss declara falha do equipamento, a crítica registra construcao/reforco/extensao de rd e a obra movimentou 1 transformador.</t>
+          <t>o dono pediu categoria própria: “Substituição de chave fusível”. A obra encerrada e conferida não movimentou transformador nenhum — o que ela trocou foi a chave. Estava caindo na categoria genérica de obra sem transformador.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00487/2026</t>
+          <t>DOLP-RD-PA 00688/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AVARIADO</t>
+          <t>Preventivo ou programado</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra queimado por sobrecarga e a obra movimentou 1 transformador. saía do indicador por estar a 28 horas da janela.</t>
+          <t>o dono mandou mover para preventivo: “mova do lugar de onde está e coloca no preventivo”. A SS não foi aberta pelo COI — foi aberta pelo DEOP, ou seja, a equipe achou o defeito antes de o cliente reclamar. O texto declara avariado e a obra movimentou transformador; o que muda não é o que aconteceu com o equipamento, é o enquadramento: troca encontrada em ronda não é falha que penalizou o indicador</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00117/2026</t>
+          <t>ENC-RD-PS 00095/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AVARIADO</t>
+          <t>Preventivo ou programado</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra arvore de pequeno/ medio porte na rede / na faixa e a obra movimentou 1 transformador. saía do indicador por estar a 691 horas da janela.</t>
+          <t>o dono mandou mover para preventivo: “mova do lugar de onde está e coloca no preventivo”. A SS não foi aberta pelo COI — foi aberta pela própria manutenção, ou seja, a equipe achou o defeito antes de o cliente reclamar. O texto declara queimado e a obra movimentou transformador; o que muda não é o que aconteceu com o equipamento, é o enquadramento: troca encontrada em ronda não é falha que penalizou o indicador</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00327/2026</t>
+          <t>ENC-RD-PS 00116/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AVARIADO</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -6270,14 +6270,14 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra vazamento de oleo / tanque deteriorado e a obra movimentou 1 transformador. saía do indicador por estar a 5 horas da janela.</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara queimado; a crítica registra causa nao identificada - especificar e a obra movimentou 1 transformador. saía do indicador por estar a 3801 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00493/2026</t>
+          <t>ENC-RD-PS 00317/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AVARIADO</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -6297,14 +6297,14 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra rd de at e a obra movimentou 1 transformador. saía do indicador por estar a 4 horas da janela.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 235 horas da janela; o texto da ss declara falha do equipamento, a crítica registra construcao/reforco/extensao de rd e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00501/2026</t>
+          <t>ENC-RD-PS 00487/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6324,41 +6324,41 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra vazamento de oleo / tanque deteriorado e a obra movimentou 1 transformador. saía do indicador por estar a 3 horas da janela.</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra queimado por sobrecarga e a obra movimentou 1 transformador. saía do indicador por estar a 28 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00587/2026</t>
+          <t>ETO-RD-AG 00117/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tape interno</t>
+          <t>AVARIADO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>o dono mandou excluir na categoria de tape. A observação da própria ocorrência conta o serviço inteiro: “Abertura emergencial do trafo 5700012065 para possibilitar alterar TAP melhoria de tensão. Ao remover a tampa do trafo, caiu dentro do oleo os parafusos. Foi aberto nota e trocado o mesmo.” O transformador foi aberto de propósito para mexer no tape; a troca veio do acidente durante o serviço, não de falha do equipamento. Nenhum texto do caso afirma queima</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra arvore de pequeno/ medio porte na rede / na faixa e a obra movimentou 1 transformador. saía do indicador por estar a 691 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00224/2026</t>
+          <t>ETO-RD-AG 00327/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>AVARIADO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -6378,14 +6378,14 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 73 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra vazamento de oleo / tanque deteriorado e a obra movimentou 1 transformador. saía do indicador por estar a 5 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00327/2026</t>
+          <t>ETO-RD-AG 00493/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>AVARIADO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -6405,68 +6405,68 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 2194 horas da janela; o texto da ss declara falha do equipamento, a crítica registra animal/passaro na rede e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra rd de at e a obra movimentou 1 transformador. saía do indicador por estar a 4 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00408/2026</t>
+          <t>ETO-RD-AG 00501/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>Preventivo ou programado</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 163 horas da janela; o texto da ss declara falha do equipamento, a crítica registra causa nao identificada - especificar e a obra movimentou 1 transformador.</t>
+          <t>o dono mandou mover para preventivo: “mova do lugar de onde está e coloca no preventivo”. A SS não foi aberta pelo COI — foi aberta pela própria manutenção, ou seja, a equipe achou o defeito antes de o cliente reclamar. O texto declara avariado e a obra movimentou transformador; o que muda não é o que aconteceu com o equipamento, é o enquadramento: troca encontrada em ronda não é falha que penalizou o indicador</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00436/2026</t>
+          <t>ETO-RD-AG 00587/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>Tape interno</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 12 horas da janela; o texto da ss declara falha do equipamento, a crítica registra queimado por causa nao identificada e a obra movimentou 1 transformador.</t>
+          <t>o dono mandou excluir na categoria de tape. A observação da própria ocorrência conta o serviço inteiro: “Abertura emergencial do trafo 5700012065 para possibilitar alterar TAP melhoria de tensão. Ao remover a tampa do trafo, caiu dentro do oleo os parafusos. Foi aberto nota e trocado o mesmo.” O transformador foi aberto de propósito para mexer no tape; a troca veio do acidente durante o serviço, não de falha do equipamento. Nenhum texto do caso afirma queima</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00468/2026</t>
+          <t>ETO-RD-AR 00033/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ausente da base de interrupções</t>
+          <t>Preventivo ou programado</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -6486,95 +6486,95 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>o dono reviu a própria decisão: “se estiver fora daquelas janelas … deverão ser excluídos”. Ele havia mandado incluir por ler queima com SIGCO incorreto; conferido na Crítica crua, o código 5301889004 não aparece em papel nenhum nos sete meses — nem com defeito, nem interrompido, nem manobrado. Nem o 5701889004 que a OS escreve, nem o 570188904 que a SS escreve. Sem registro de interrupção não há evento a medir</t>
+          <t>o dono mandou mover para preventivo: “mova do lugar de onde está e coloca no preventivo”. A SS não foi aberta pelo COI — foi aberta pela própria manutenção, ou seja, a equipe achou o defeito antes de o cliente reclamar. O texto declara queimado e a obra movimentou transformador; o que muda não é o que aconteceu com o equipamento, é o enquadramento: troca encontrada em ronda não é falha que penalizou o indicador</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00604/2026</t>
+          <t>ETO-RD-AR 00172/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>Preventivo ou programado</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 2 horas da janela; o texto da ss declara falha do equipamento, a crítica registra falha bucha de bt e a obra movimentou 1 transformador.</t>
+          <t>o dono mandou mover para preventivo: “mova do lugar de onde está e coloca no preventivo”. A SS não foi aberta pelo COI — foi aberta pela própria manutenção, ou seja, a equipe achou o defeito antes de o cliente reclamar. O texto declara queimado e a obra movimentou transformador; o que muda não é o que aconteceu com o equipamento, é o enquadramento: troca encontrada em ronda não é falha que penalizou o indicador</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00692/2026</t>
+          <t>ETO-RD-AR 00224/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avaliar com o Matheus</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>o dono mandou tirar do indicador e marcar para avaliar com o Matheus. O caso tem três vozes e elas não fecham: a SS escreve “QUEIMADO AVARIADO” — as duas palavras, na mesma linha —, a obra foi aberta como substituição de trafo avariado, e o custo entrou no projeto SIGCO 8495, que é de avaria. Fica fora da conta enquanto a avaliação não decidir qual das três vale</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 73 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00739/2026</t>
+          <t>ETO-RD-AR 00327/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cola e fita — reparo, não troca</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>o dono achou o caso que procurava desde o começo da revisão: “finalmente um caso de cola e fita, exclua ele e classifique como cola e fita”. A OS conta o serviço inteiro — “FEITO COLAGEM E VEDAÇÃO NA BUCHA DO TRAFO 5743290004 QUE ESTAVA COM VAZAMENTO” —, e nenhum transformador foi movimentado: a SS e a OS não trazem série nem tombamento de retirado e instalado. Não houve troca, houve reparo</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 2194 horas da janela; o texto da ss declara falha do equipamento, a crítica registra animal/passaro na rede e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00740/2026</t>
+          <t>ETO-RD-AR 00408/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6594,68 +6594,68 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1073 horas da janela; o texto da ss declara falha do equipamento, a crítica registra elo subdimensionado e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 163 horas da janela; o texto da ss declara falha do equipamento, a crítica registra causa nao identificada - especificar e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 01030/2026</t>
+          <t>ETO-RD-AR 00436/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tape interno</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>o dono leu o caso e mandou excluir na categoria de tape interno. A OS registra o tape do retirado na posição 05 e o do instalado na 04: a troca moveu o tape, e o tape é interno — não se ajusta em campo. Vale só para este caso: a mesma diferença de posição aparece em 236 das 1.510 e não sustenta regra.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 12 horas da janela; o texto da ss declara falha do equipamento, a crítica registra queimado por causa nao identificada e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ETO-RD-DP 00115/2026</t>
+          <t>ETO-RD-AR 00468/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>Ausente da base de interrupções</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1437 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+          <t>o dono reviu a própria decisão: “se estiver fora daquelas janelas … deverão ser excluídos”. Ele havia mandado incluir por ler queima com SIGCO incorreto; conferido na Crítica crua, o código 5301889004 não aparece em papel nenhum nos sete meses — nem com defeito, nem interrompido, nem manobrado. Nem o 5701889004 que a OS escreve, nem o 570188904 que a SS escreve. Sem registro de interrupção não há evento a medir</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ETO-RD-DP 00156/2026</t>
+          <t>ETO-RD-AR 00604/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6675,14 +6675,14 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>O dono reviu e mandou de volta para a saída como queimado, mantendo a marca: “esse da meta por último também leva para saída de queimado porém coloca essa classificação”. a os diz “transformador substituido pela meta” e a obra está registrada noutra empreiteira — quem executou não é quem o cadastro contratou. isso é etiqueta, não causa: o transformador queimou do mesmo jeito.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 2 horas da janela; o texto da ss declara falha do equipamento, a crítica registra falha bucha de bt e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ETO-RD-DP 00182/2026</t>
+          <t>ETO-RD-AR 00692/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Furto, roubo ou vandalismo</t>
+          <t>Avaliar com o Matheus</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>o dono mandou excluir como furto. A SS e a OS são idênticas e explícitas: “Constatado trafo 5700273116 de 15kVA na 19.9kV e para-raios furtados. Acesso bom.” O gatilho de furto já estava aceso e o caso chegava à saída assim mesmo — a codificação da Crítica diz queima, mas a observação dela não descreve sintoma nenhum, e quem esteve no poste escreveu furto</t>
+          <t>o dono mandou tirar do indicador e marcar para avaliar com o Matheus. O caso tem três vozes e elas não fecham: a SS escreve “QUEIMADO AVARIADO” — as duas palavras, na mesma linha —, a obra foi aberta como substituição de trafo avariado, e o custo entrou no projeto SIGCO 8495, que é de avaria. Fica fora da conta enquanto a avaliação não decidir qual das três vale</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00167/2026</t>
+          <t>ETO-RD-AR 00739/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>Cola e fita — reparo, não troca</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara queimado; a crítica registra descarga atmosferica e a obra movimentou 1 transformador. saía do indicador por estar a 24 horas da janela.</t>
+          <t>o dono achou o caso que procurava desde o começo da revisão: “finalmente um caso de cola e fita, exclua ele e classifique como cola e fita”. A OS conta o serviço inteiro — “FEITO COLAGEM E VEDAÇÃO NA BUCHA DO TRAFO 5743290004 QUE ESTAVA COM VAZAMENTO” —, e nenhum transformador foi movimentado: a SS e a OS não trazem série nem tombamento de retirado e instalado. Não houve troca, houve reparo</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00199/2026</t>
+          <t>ETO-RD-AR 00740/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6756,68 +6756,68 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1165 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1073 horas da janela; o texto da ss declara falha do equipamento, a crítica registra elo subdimensionado e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00208/2026</t>
+          <t>ETO-RD-AR 00820/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>Preventivo ou programado</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1102 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+          <t>o dono mandou mover para preventivo: “mova do lugar de onde está e coloca no preventivo”. A SS não foi aberta pelo COI — foi aberta pela própria manutenção, ou seja, a equipe achou o defeito antes de o cliente reclamar. O texto declara queimado e a obra movimentou transformador; o que muda não é o que aconteceu com o equipamento, é o enquadramento: troca encontrada em ronda não é falha que penalizou o indicador</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00278/2026</t>
+          <t>ETO-RD-AR 01030/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AVARIADO</t>
+          <t>Tape interno</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra descarga atmosferica e a obra movimentou 1 transformador. saía do indicador por estar a 142 horas da janela.</t>
+          <t>o dono leu o caso e mandou excluir na categoria de tape interno. A OS registra o tape do retirado na posição 05 e o do instalado na 04: a troca moveu o tape, e o tape é interno — não se ajusta em campo. Vale só para este caso: a mesma diferença de posição aparece em 236 das 1.510 e não sustenta regra.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00279/2026</t>
+          <t>ETO-RD-DP 00115/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6837,14 +6837,14 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>O dono martelou queimado e mandou marcar o zero: “queimado e classifica com zero clientes interrompidos”. a crítica registra a ocorrência 20264137433112 com defeito no próprio transformador e a ss abrindo dentro do intervalo dela — fato pleno —, mas nenhum cliente foi interrompido, e a obra 0712600198 está fora do export de material. entra pelo campo e pelo texto, com as duas marcas escritas na linha.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1437 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00324/2026</t>
+          <t>ETO-RD-DP 00156/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AVARIADO</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6864,41 +6864,41 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra vazamento de oleo / tanque deteriorado e a obra movimentou 1 transformador. saía do indicador por estar a 15 horas da janela.</t>
+          <t>O dono reviu e mandou de volta para a saída como queimado, mantendo a marca: “esse da meta por último também leva para saída de queimado porém coloca essa classificação”. a os diz “transformador substituido pela meta” e a obra está registrada noutra empreiteira — quem executou não é quem o cadastro contratou. isso é etiqueta, não causa: o transformador queimou do mesmo jeito.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00373/2026</t>
+          <t>ETO-RD-DP 00182/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AVARIADO</t>
+          <t>Furto, roubo ou vandalismo</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra descarga atmosferica e a obra movimentou 1 transformador. saía do indicador por estar a 166 horas da janela.</t>
+          <t>o dono mandou excluir como furto. A SS e a OS são idênticas e explícitas: “Constatado trafo 5700273116 de 15kVA na 19.9kV e para-raios furtados. Acesso bom.” O gatilho de furto já estava aceso e o caso chegava à saída assim mesmo — a codificação da Crítica diz queima, mas a observação dela não descreve sintoma nenhum, e quem esteve no poste escreveu furto</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00405/2026</t>
+          <t>ETO-RD-GR 00167/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6918,41 +6918,41 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 5 horas da janela; o texto da ss declara falha do equipamento, a crítica registra falha bucha de bt e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara queimado; a crítica registra descarga atmosferica e a obra movimentou 1 transformador. saía do indicador por estar a 24 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00534/2026</t>
+          <t>ETO-RD-GR 00199/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cola e fita — reparo, não troca</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>o dono mandou mudar para cola e fita, e o campo confirma sem depender de leitura: a base de SS e OS grava DEFEITO = “COLA E FITA” neste caso — preenchido depois da execução, é o que a equipe fechou. A OS diz “REPARO EM TRAFO COM VAZAMENTO DE ÓLEO” e a obra encerrada e conferida não movimentou transformador nenhum. A SS pediu substituição com aumento de potência; o que se fez foi reparo</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1165 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ETO-RD-GU 00058/2026</t>
+          <t>ETO-RD-GR 00208/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6972,14 +6972,14 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 19 horas da janela; o texto da ss declara falha do equipamento, a crítica registra rd de at e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1102 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ETO-RD-GU 00061/2026</t>
+          <t>ETO-RD-GR 00278/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6989,7 +6989,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>AVARIADO</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6999,41 +6999,41 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 2561 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra descarga atmosferica e a obra movimentou 1 transformador. saía do indicador por estar a 142 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ETO-RD-GU 00179/2026</t>
+          <t>ETO-RD-GR 00279/2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Furto, roubo ou vandalismo</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>o dono mandou excluir como furto, confirmando o que quatro registros independentes de campo já diziam: o SIGCO da obra é 61993 “FURTO DE BENS TRAFO”, a SS traz Origem e Defeito gravados como FURTADO, a Crítica registra observação “transformador furtado” com ZERO cliente interrompido nos dois passos, e o texto da SS diz “transformador e medidor furtado”. A subcausa “queimado por descarga atmosférica” é codificação genérica do despachante, e não descreve o que a equipe achou</t>
+          <t>O dono martelou queimado e mandou marcar o zero: “queimado e classifica com zero clientes interrompidos”. a crítica registra a ocorrência 20264137433112 com defeito no próprio transformador e a ss abrindo dentro do intervalo dela — fato pleno —, mas nenhum cliente foi interrompido, e a obra 0712600198 está fora do export de material. entra pelo campo e pelo texto, com as duas marcas escritas na linha.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ETO-RD-GU 00305/2026</t>
+          <t>ETO-RD-GR 00324/2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>AVARIADO</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7053,32 +7053,221 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 243 horas da janela; o texto da ss declara falha do equipamento, a crítica registra partido na fase e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra vazamento de oleo / tanque deteriorado e a obra movimentou 1 transformador. saía do indicador por estar a 15 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>ETO-RD-GR 00373/2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AVARIADO</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra descarga atmosferica e a obra movimentou 1 transformador. saía do indicador por estar a 166 horas da janela.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00405/2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 5 horas da janela; o texto da ss declara falha do equipamento, a crítica registra falha bucha de bt e a obra movimentou 1 transformador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00534/2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>EXCLUIR</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Cola e fita — reparo, não troca</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>EXCLUÍDA</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>o dono mandou mudar para cola e fita, e o campo confirma sem depender de leitura: a base de SS e OS grava DEFEITO = “COLA E FITA” neste caso — preenchido depois da execução, é o que a equipe fechou. A OS diz “REPARO EM TRAFO COM VAZAMENTO DE ÓLEO” e a obra encerrada e conferida não movimentou transformador nenhum. A SS pediu substituição com aumento de potência; o que se fez foi reparo</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ETO-RD-GU 00058/2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 19 horas da janela; o texto da ss declara falha do equipamento, a crítica registra rd de at e a obra movimentou 1 transformador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ETO-RD-GU 00061/2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 2561 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ETO-RD-GU 00179/2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>EXCLUIR</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Furto, roubo ou vandalismo</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>EXCLUÍDA</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>o dono mandou excluir como furto, confirmando o que quatro registros independentes de campo já diziam: o SIGCO da obra é 61993 “FURTO DE BENS TRAFO”, a SS traz Origem e Defeito gravados como FURTADO, a Crítica registra observação “transformador furtado” com ZERO cliente interrompido nos dois passos, e o texto da SS diz “transformador e medidor furtado”. A subcausa “queimado por descarga atmosférica” é codificação genérica do despachante, e não descreve o que a equipe achou</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ETO-RD-GU 00305/2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 243 horas da janela; o texto da ss declara falha do equipamento, a crítica registra partido na fase e a obra movimentou 1 transformador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>ETO-RD-GU 00685/2026</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>EXCLUIR</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Abalroamento</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>EXCLUÍDA</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>o dono mandou mover para abalroamento, e as quatro vozes concordam com ele: a Crítica registra causa POSTE DE AT e subcausa ABALROADO, o TMAE repete as duas, a SS foi gravada como ABALROAMENTO e a obra 0412600528 entra no SIGCO 20497 — DANOS CAUSADOS POR TERCEIROS. O caso saía como obra de poste por segurança, que é outra coisa: segurança é a companhia decidindo trocar um poste, abalroamento é um terceiro derrubando. A diferença muda para onde o custo vai — ressarcimento, não manutenção</t>
         </is>

--- a/auditoria-transformadores-134/public/bases/Base_Funis.xlsx
+++ b/auditoria-transformadores-134/public/bases/Base_Funis.xlsx
@@ -526,10 +526,10 @@
         <v>1510</v>
       </c>
       <c r="D5" t="n">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E5" t="n">
-        <v>1294</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="6">
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1294</v>
+        <v>1290</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1294</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="7">
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1294</v>
+        <v>1290</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1294</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="8">
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1294</v>
+        <v>1290</v>
       </c>
       <c r="D8" t="n">
         <v>21</v>
       </c>
       <c r="E8" t="n">
-        <v>1273</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="9">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1273</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="10">
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1273</v>
+        <v>1269</v>
       </c>
     </row>
   </sheetData>
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -819,39 +819,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MONTE DO CARMO</t>
+          <t>DIVINOPOLIS DO TOCANTINS</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DIVINOPOLIS DO TOCANTINS</t>
+          <t>MONTE DO CARMO</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>23</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
         <v>24</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -914,17 +914,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARAGUACEMA</t>
+          <t>GOIATINS</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>22</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>26</v>
@@ -933,17 +933,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GOIATINS</t>
+          <t>ARAGUACEMA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" t="n">
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>26</v>
@@ -1712,64 +1712,64 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BABACULANDIA</t>
+          <t>DARCINOPOLIS</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C57" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DARCINOPOLIS</t>
+          <t>ALIANCA DO TOCANTINS</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>8</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ALIANCA DO TOCANTINS</t>
+          <t>PALMEIRANTE</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>8</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PALMEIRANTE</t>
+          <t>MURICILANDIA</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1788,96 +1788,96 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MURICILANDIA</t>
+          <t>MONTE SANTO DO TOCANTINS</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>8</v>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MONTE SANTO DO TOCANTINS</t>
+          <t>CAMPOS LINDOS</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>8</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CAMPOS LINDOS</t>
+          <t>LAGOA DA CONFUSAO</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>8</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LAGOA DA CONFUSAO</t>
+          <t>ARAGUANA</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>8</v>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ARAGUANA</t>
+          <t>BABACULANDIA</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>8</v>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66">
@@ -3363,11 +3363,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1202</v>
+        <v>1198</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>79.3%</t>
         </is>
       </c>
     </row>
@@ -3393,11 +3393,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>84.0%</t>
         </is>
       </c>
     </row>
@@ -3408,11 +3408,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.6%</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>216 exclusões em 23 categorias, e elas se dividem em duas famílias que convém não misturar: 105 não têm interrupção que sustente o caso e 111 têm causa ou documento fora do indicador.</t>
+          <t>220 exclusões em 23 categorias, e elas se dividem em duas famílias que convém não misturar: 108 não têm interrupção que sustente o caso e 112 têm causa ou documento fora do indicador.</t>
         </is>
       </c>
     </row>
@@ -3523,11 +3523,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3548,11 +3548,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3764,12 +3764,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Falta de fase interna</t>
+          <t>Possível erro de cadastro do código</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>falta_fase</t>
+          <t>erro_cadastro</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3789,12 +3789,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Auxiliar de religador ou regulador</t>
+          <t>Falta de fase interna</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>auxiliar</t>
+          <t>falta_fase</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3814,12 +3814,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Divisão de circuito</t>
+          <t>Auxiliar de religador ou regulador</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>divisao</t>
+          <t>auxiliar</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3839,12 +3839,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cola e fita — reparo, não troca</t>
+          <t>Divisão de circuito</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>cola_fita</t>
+          <t>divisao</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3864,12 +3864,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Desativação do posto</t>
+          <t>Cola e fita — reparo, não troca</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>desativacao</t>
+          <t>cola_fita</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3889,20 +3889,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Obra aberta que não executou nada</t>
+          <t>Desativação do posto</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>obra_sem_execucao</t>
+          <t>desativacao</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3914,12 +3914,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Causada por terceiros</t>
+          <t>Obra aberta que não executou nada</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>terceiros</t>
+          <t>obra_sem_execucao</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3939,12 +3939,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Possível erro de cadastro do código</t>
+          <t>Causada por terceiros</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>erro_cadastro</t>
+          <t>terceiros</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>1283</v>
       </c>
       <c r="C4" t="n">
-        <v>1207</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="5">
@@ -4271,7 +4271,7 @@
         <v>123</v>
       </c>
       <c r="C5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6">
@@ -4297,7 +4297,7 @@
         <v>26</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5764,12 +5764,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
@@ -6277,34 +6277,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00317/2026</t>
+          <t>ENC-RD-PS 00246/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>Ausente da base de interrupções</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 235 horas da janela; o texto da ss declara falha do equipamento, a crítica registra construcao/reforco/extensao de rd e a obra movimentou 1 transformador.</t>
+          <t>o dono mandou mover para ausente da base de interrupções. Conferido na Crítica crua: o código 5720337055 nunca teve defeito aberto nele em data nenhuma dos sete meses — aparece uma vez, e só como manobrado. O caso entrava pelo TMAE, não pela Crítica: era um F0, atendimento no código do trafo sem ocorrência que o sustentasse</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00487/2026</t>
+          <t>ENC-RD-PS 00317/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AVARIADO</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -6324,14 +6324,14 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra queimado por sobrecarga e a obra movimentou 1 transformador. saía do indicador por estar a 28 horas da janela.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 235 horas da janela; o texto da ss declara falha do equipamento, a crítica registra construcao/reforco/extensao de rd e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00117/2026</t>
+          <t>ENC-RD-PS 00487/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6351,14 +6351,14 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra arvore de pequeno/ medio porte na rede / na faixa e a obra movimentou 1 transformador. saía do indicador por estar a 691 horas da janela.</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra queimado por sobrecarga e a obra movimentou 1 transformador. saía do indicador por estar a 28 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00327/2026</t>
+          <t>ETO-RD-AG 00117/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6378,14 +6378,14 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra vazamento de oleo / tanque deteriorado e a obra movimentou 1 transformador. saía do indicador por estar a 5 horas da janela.</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra arvore de pequeno/ medio porte na rede / na faixa e a obra movimentou 1 transformador. saía do indicador por estar a 691 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00493/2026</t>
+          <t>ETO-RD-AG 00327/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6405,41 +6405,41 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra rd de at e a obra movimentou 1 transformador. saía do indicador por estar a 4 horas da janela.</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra vazamento de oleo / tanque deteriorado e a obra movimentou 1 transformador. saía do indicador por estar a 5 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00501/2026</t>
+          <t>ETO-RD-AG 00493/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Preventivo ou programado</t>
+          <t>AVARIADO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>o dono mandou mover para preventivo: “mova do lugar de onde está e coloca no preventivo”. A SS não foi aberta pelo COI — foi aberta pela própria manutenção, ou seja, a equipe achou o defeito antes de o cliente reclamar. O texto declara avariado e a obra movimentou transformador; o que muda não é o que aconteceu com o equipamento, é o enquadramento: troca encontrada em ronda não é falha que penalizou o indicador</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra rd de at e a obra movimentou 1 transformador. saía do indicador por estar a 4 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00587/2026</t>
+          <t>ETO-RD-AG 00501/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tape interno</t>
+          <t>Preventivo ou programado</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -6459,14 +6459,14 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>o dono mandou excluir na categoria de tape. A observação da própria ocorrência conta o serviço inteiro: “Abertura emergencial do trafo 5700012065 para possibilitar alterar TAP melhoria de tensão. Ao remover a tampa do trafo, caiu dentro do oleo os parafusos. Foi aberto nota e trocado o mesmo.” O transformador foi aberto de propósito para mexer no tape; a troca veio do acidente durante o serviço, não de falha do equipamento. Nenhum texto do caso afirma queima</t>
+          <t>o dono mandou mover para preventivo: “mova do lugar de onde está e coloca no preventivo”. A SS não foi aberta pelo COI — foi aberta pela própria manutenção, ou seja, a equipe achou o defeito antes de o cliente reclamar. O texto declara avariado e a obra movimentou transformador; o que muda não é o que aconteceu com o equipamento, é o enquadramento: troca encontrada em ronda não é falha que penalizou o indicador</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00033/2026</t>
+          <t>ETO-RD-AG 00587/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Preventivo ou programado</t>
+          <t>Tape interno</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -6486,14 +6486,14 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>o dono mandou mover para preventivo: “mova do lugar de onde está e coloca no preventivo”. A SS não foi aberta pelo COI — foi aberta pela própria manutenção, ou seja, a equipe achou o defeito antes de o cliente reclamar. O texto declara queimado e a obra movimentou transformador; o que muda não é o que aconteceu com o equipamento, é o enquadramento: troca encontrada em ronda não é falha que penalizou o indicador</t>
+          <t>o dono mandou excluir na categoria de tape. A observação da própria ocorrência conta o serviço inteiro: “Abertura emergencial do trafo 5700012065 para possibilitar alterar TAP melhoria de tensão. Ao remover a tampa do trafo, caiu dentro do oleo os parafusos. Foi aberto nota e trocado o mesmo.” O transformador foi aberto de propósito para mexer no tape; a troca veio do acidente durante o serviço, não de falha do equipamento. Nenhum texto do caso afirma queima</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00172/2026</t>
+          <t>ETO-RD-AR 00033/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6520,34 +6520,34 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00224/2026</t>
+          <t>ETO-RD-AR 00172/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>Preventivo ou programado</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 73 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+          <t>o dono mandou mover para preventivo: “mova do lugar de onde está e coloca no preventivo”. A SS não foi aberta pelo COI — foi aberta pela própria manutenção, ou seja, a equipe achou o defeito antes de o cliente reclamar. O texto declara queimado e a obra movimentou transformador; o que muda não é o que aconteceu com o equipamento, é o enquadramento: troca encontrada em ronda não é falha que penalizou o indicador</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00327/2026</t>
+          <t>ETO-RD-AR 00224/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6567,14 +6567,14 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 2194 horas da janela; o texto da ss declara falha do equipamento, a crítica registra animal/passaro na rede e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 73 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00408/2026</t>
+          <t>ETO-RD-AR 00327/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6594,14 +6594,14 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 163 horas da janela; o texto da ss declara falha do equipamento, a crítica registra causa nao identificada - especificar e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 2194 horas da janela; o texto da ss declara falha do equipamento, a crítica registra animal/passaro na rede e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00436/2026</t>
+          <t>ETO-RD-AR 00408/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6621,95 +6621,95 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 12 horas da janela; o texto da ss declara falha do equipamento, a crítica registra queimado por causa nao identificada e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 163 horas da janela; o texto da ss declara falha do equipamento, a crítica registra causa nao identificada - especificar e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00468/2026</t>
+          <t>ETO-RD-AR 00436/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ausente da base de interrupções</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>o dono reviu a própria decisão: “se estiver fora daquelas janelas … deverão ser excluídos”. Ele havia mandado incluir por ler queima com SIGCO incorreto; conferido na Crítica crua, o código 5301889004 não aparece em papel nenhum nos sete meses — nem com defeito, nem interrompido, nem manobrado. Nem o 5701889004 que a OS escreve, nem o 570188904 que a SS escreve. Sem registro de interrupção não há evento a medir</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 12 horas da janela; o texto da ss declara falha do equipamento, a crítica registra queimado por causa nao identificada e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00604/2026</t>
+          <t>ETO-RD-AR 00468/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>Ausente da base de interrupções</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 2 horas da janela; o texto da ss declara falha do equipamento, a crítica registra falha bucha de bt e a obra movimentou 1 transformador.</t>
+          <t>o dono reviu a própria decisão: “se estiver fora daquelas janelas … deverão ser excluídos”. Ele havia mandado incluir por ler queima com SIGCO incorreto; conferido na Crítica crua, o código 5301889004 não aparece em papel nenhum nos sete meses — nem com defeito, nem interrompido, nem manobrado. Nem o 5701889004 que a OS escreve, nem o 570188904 que a SS escreve. Sem registro de interrupção não há evento a medir</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00692/2026</t>
+          <t>ETO-RD-AR 00604/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avaliar com o Matheus</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>o dono mandou tirar do indicador e marcar para avaliar com o Matheus. O caso tem três vozes e elas não fecham: a SS escreve “QUEIMADO AVARIADO” — as duas palavras, na mesma linha —, a obra foi aberta como substituição de trafo avariado, e o custo entrou no projeto SIGCO 8495, que é de avaria. Fica fora da conta enquanto a avaliação não decidir qual das três vale</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 2 horas da janela; o texto da ss declara falha do equipamento, a crítica registra falha bucha de bt e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00739/2026</t>
+          <t>ETO-RD-AR 00692/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cola e fita — reparo, não troca</t>
+          <t>Avaliar com o Matheus</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6729,41 +6729,41 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>o dono achou o caso que procurava desde o começo da revisão: “finalmente um caso de cola e fita, exclua ele e classifique como cola e fita”. A OS conta o serviço inteiro — “FEITO COLAGEM E VEDAÇÃO NA BUCHA DO TRAFO 5743290004 QUE ESTAVA COM VAZAMENTO” —, e nenhum transformador foi movimentado: a SS e a OS não trazem série nem tombamento de retirado e instalado. Não houve troca, houve reparo</t>
+          <t>o dono mandou tirar do indicador e marcar para avaliar com o Matheus. O caso tem três vozes e elas não fecham: a SS escreve “QUEIMADO AVARIADO” — as duas palavras, na mesma linha —, a obra foi aberta como substituição de trafo avariado, e o custo entrou no projeto SIGCO 8495, que é de avaria. Fica fora da conta enquanto a avaliação não decidir qual das três vale</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00740/2026</t>
+          <t>ETO-RD-AR 00702/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>Ausente da base de interrupções</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1073 horas da janela; o texto da ss declara falha do equipamento, a crítica registra elo subdimensionado e a obra movimentou 1 transformador.</t>
+          <t>o dono mandou mover para ausente da base de interrupções. Conferido na Crítica crua: o código 5701086022 nunca teve defeito aberto nele em data nenhuma — aparece uma vez, e só como manobrado. Entrava pelo TMAE, e o próprio atendimento registra causa CHAVE FUSIVEL/RELIGADORA com subcausa porta-fusível danificado, não falha do transformador</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00820/2026</t>
+          <t>ETO-RD-AR 00739/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Preventivo ou programado</t>
+          <t>Cola e fita — reparo, não troca</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6783,122 +6783,122 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>o dono mandou mover para preventivo: “mova do lugar de onde está e coloca no preventivo”. A SS não foi aberta pelo COI — foi aberta pela própria manutenção, ou seja, a equipe achou o defeito antes de o cliente reclamar. O texto declara queimado e a obra movimentou transformador; o que muda não é o que aconteceu com o equipamento, é o enquadramento: troca encontrada em ronda não é falha que penalizou o indicador</t>
+          <t>o dono achou o caso que procurava desde o começo da revisão: “finalmente um caso de cola e fita, exclua ele e classifique como cola e fita”. A OS conta o serviço inteiro — “FEITO COLAGEM E VEDAÇÃO NA BUCHA DO TRAFO 5743290004 QUE ESTAVA COM VAZAMENTO” —, e nenhum transformador foi movimentado: a SS e a OS não trazem série nem tombamento de retirado e instalado. Não houve troca, houve reparo</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 01030/2026</t>
+          <t>ETO-RD-AR 00740/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tape interno</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>o dono leu o caso e mandou excluir na categoria de tape interno. A OS registra o tape do retirado na posição 05 e o do instalado na 04: a troca moveu o tape, e o tape é interno — não se ajusta em campo. Vale só para este caso: a mesma diferença de posição aparece em 236 das 1.510 e não sustenta regra.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1073 horas da janela; o texto da ss declara falha do equipamento, a crítica registra elo subdimensionado e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ETO-RD-DP 00115/2026</t>
+          <t>ETO-RD-AR 00820/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>Preventivo ou programado</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1437 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+          <t>o dono mandou mover para preventivo: “mova do lugar de onde está e coloca no preventivo”. A SS não foi aberta pelo COI — foi aberta pela própria manutenção, ou seja, a equipe achou o defeito antes de o cliente reclamar. O texto declara queimado e a obra movimentou transformador; o que muda não é o que aconteceu com o equipamento, é o enquadramento: troca encontrada em ronda não é falha que penalizou o indicador</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ETO-RD-DP 00156/2026</t>
+          <t>ETO-RD-AR 01030/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>Tape interno</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>O dono reviu e mandou de volta para a saída como queimado, mantendo a marca: “esse da meta por último também leva para saída de queimado porém coloca essa classificação”. a os diz “transformador substituido pela meta” e a obra está registrada noutra empreiteira — quem executou não é quem o cadastro contratou. isso é etiqueta, não causa: o transformador queimou do mesmo jeito.</t>
+          <t>o dono leu o caso e mandou excluir na categoria de tape interno. A OS registra o tape do retirado na posição 05 e o do instalado na 04: a troca moveu o tape, e o tape é interno — não se ajusta em campo. Vale só para este caso: a mesma diferença de posição aparece em 236 das 1.510 e não sustenta regra.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ETO-RD-DP 00182/2026</t>
+          <t>ETO-RD-DP 00115/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Furto, roubo ou vandalismo</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>o dono mandou excluir como furto. A SS e a OS são idênticas e explícitas: “Constatado trafo 5700273116 de 15kVA na 19.9kV e para-raios furtados. Acesso bom.” O gatilho de furto já estava aceso e o caso chegava à saída assim mesmo — a codificação da Crítica diz queima, mas a observação dela não descreve sintoma nenhum, e quem esteve no poste escreveu furto</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1437 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00167/2026</t>
+          <t>ETO-RD-DP 00156/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6918,41 +6918,41 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara queimado; a crítica registra descarga atmosferica e a obra movimentou 1 transformador. saía do indicador por estar a 24 horas da janela.</t>
+          <t>O dono reviu e mandou de volta para a saída como queimado, mantendo a marca: “esse da meta por último também leva para saída de queimado porém coloca essa classificação”. a os diz “transformador substituido pela meta” e a obra está registrada noutra empreiteira — quem executou não é quem o cadastro contratou. isso é etiqueta, não causa: o transformador queimou do mesmo jeito.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00199/2026</t>
+          <t>ETO-RD-DP 00182/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>Furto, roubo ou vandalismo</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1165 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+          <t>o dono mandou excluir como furto. A SS e a OS são idênticas e explícitas: “Constatado trafo 5700273116 de 15kVA na 19.9kV e para-raios furtados. Acesso bom.” O gatilho de furto já estava aceso e o caso chegava à saída assim mesmo — a codificação da Crítica diz queima, mas a observação dela não descreve sintoma nenhum, e quem esteve no poste escreveu furto</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00208/2026</t>
+          <t>ETO-RD-GR 00167/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6972,14 +6972,14 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1102 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara queimado; a crítica registra descarga atmosferica e a obra movimentou 1 transformador. saía do indicador por estar a 24 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00278/2026</t>
+          <t>ETO-RD-GR 00199/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6989,7 +6989,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AVARIADO</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6999,14 +6999,14 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra descarga atmosferica e a obra movimentou 1 transformador. saía do indicador por estar a 142 horas da janela.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1165 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00279/2026</t>
+          <t>ETO-RD-GR 00208/2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -7026,14 +7026,14 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>O dono martelou queimado e mandou marcar o zero: “queimado e classifica com zero clientes interrompidos”. a crítica registra a ocorrência 20264137433112 com defeito no próprio transformador e a ss abrindo dentro do intervalo dela — fato pleno —, mas nenhum cliente foi interrompido, e a obra 0712600198 está fora do export de material. entra pelo campo e pelo texto, com as duas marcas escritas na linha.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 1102 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00324/2026</t>
+          <t>ETO-RD-GR 00278/2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7053,14 +7053,14 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra vazamento de oleo / tanque deteriorado e a obra movimentou 1 transformador. saía do indicador por estar a 15 horas da janela.</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra descarga atmosferica e a obra movimentou 1 transformador. saía do indicador por estar a 142 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00373/2026</t>
+          <t>ETO-RD-GR 00279/2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AVARIADO</t>
+          <t>QUEIMADO</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7080,14 +7080,14 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra descarga atmosferica e a obra movimentou 1 transformador. saía do indicador por estar a 166 horas da janela.</t>
+          <t>O dono martelou queimado e mandou marcar o zero: “queimado e classifica com zero clientes interrompidos”. a crítica registra a ocorrência 20264137433112 com defeito no próprio transformador e a ss abrindo dentro do intervalo dela — fato pleno —, mas nenhum cliente foi interrompido, e a obra 0712600198 está fora do export de material. entra pelo campo e pelo texto, com as duas marcas escritas na linha.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00405/2026</t>
+          <t>ETO-RD-GR 00324/2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>AVARIADO</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7107,41 +7107,41 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 5 horas da janela; o texto da ss declara falha do equipamento, a crítica registra falha bucha de bt e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra vazamento de oleo / tanque deteriorado e a obra movimentou 1 transformador. saía do indicador por estar a 15 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00534/2026</t>
+          <t>ETO-RD-GR 00373/2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EXCLUIR</t>
+          <t>INCLUIR</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cola e fita — reparo, não troca</t>
+          <t>AVARIADO</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>o dono mandou mudar para cola e fita, e o campo confirma sem depender de leitura: a base de SS e OS grava DEFEITO = “COLA E FITA” neste caso — preenchido depois da execução, é o que a equipe fechou. A OS diz “REPARO EM TRAFO COM VAZAMENTO DE ÓLEO” e a obra encerrada e conferida não movimentou transformador nenhum. A SS pediu substituição com aumento de potência; o que se fez foi reparo</t>
+          <t>O dono mandou mover: “mova eles de onde estão para queima e avaria”. a natureza sai do texto do próprio caso, que declara avariado; a crítica registra descarga atmosferica e a obra movimentou 1 transformador. saía do indicador por estar a 166 horas da janela.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ETO-RD-GU 00058/2026</t>
+          <t>ETO-RD-GR 00405/2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7161,41 +7161,41 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 19 horas da janela; o texto da ss declara falha do equipamento, a crítica registra rd de at e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 5 horas da janela; o texto da ss declara falha do equipamento, a crítica registra falha bucha de bt e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ETO-RD-GU 00061/2026</t>
+          <t>ETO-RD-GR 00534/2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>INCLUIR</t>
+          <t>EXCLUIR</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>QUEIMADO</t>
+          <t>Cola e fita — reparo, não troca</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SAÍDA</t>
+          <t>EXCLUÍDA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 2561 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+          <t>o dono mandou mudar para cola e fita, e o campo confirma sem depender de leitura: a base de SS e OS grava DEFEITO = “COLA E FITA” neste caso — preenchido depois da execução, é o que a equipe fechou. A OS diz “REPARO EM TRAFO COM VAZAMENTO DE ÓLEO” e a obra encerrada e conferida não movimentou transformador nenhum. A SS pediu substituição com aumento de potência; o que se fez foi reparo</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ETO-RD-GU 00179/2026</t>
+          <t>ETO-RD-GU 00017/2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Furto, roubo ou vandalismo</t>
+          <t>Ausente da base · registro em outra data</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7215,14 +7215,14 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>o dono mandou excluir como furto, confirmando o que quatro registros independentes de campo já diziam: o SIGCO da obra é 61993 “FURTO DE BENS TRAFO”, a SS traz Origem e Defeito gravados como FURTADO, a Crítica registra observação “transformador furtado” com ZERO cliente interrompido nos dois passos, e o texto da SS diz “transformador e medidor furtado”. A subcausa “queimado por descarga atmosférica” é codificação genérica do despachante, e não descreve o que a equipe achou</t>
+          <t>o dono mandou os três para ausente da base de interrupções, e para este a Crítica não deixa: o código 5701363094 TEM defeito aberto nele, na ocorrência 20254026190596 de 15/12/2025, subcausa partido na fase — dezenove dias antes desta SS. Não é ausente; é fora da janela, que é a categoria de quem tem registro próprio em outra data. Sai do indicador do mesmo jeito, com o nome que a base sustenta</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ETO-RD-GU 00305/2026</t>
+          <t>ETO-RD-GU 00058/2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7242,32 +7242,113 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 243 horas da janela; o texto da ss declara falha do equipamento, a crítica registra partido na fase e a obra movimentou 1 transformador.</t>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 19 horas da janela; o texto da ss declara falha do equipamento, a crítica registra rd de at e a obra movimentou 1 transformador.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>ETO-RD-GU 00061/2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 2561 horas da janela; o texto da ss declara falha do equipamento, a crítica registra descarga atmosferica e a obra movimentou 1 transformador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ETO-RD-GU 00179/2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>EXCLUIR</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Furto, roubo ou vandalismo</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>EXCLUÍDA</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>o dono mandou excluir como furto, confirmando o que quatro registros independentes de campo já diziam: o SIGCO da obra é 61993 “FURTO DE BENS TRAFO”, a SS traz Origem e Defeito gravados como FURTADO, a Crítica registra observação “transformador furtado” com ZERO cliente interrompido nos dois passos, e o texto da SS diz “transformador e medidor furtado”. A subcausa “queimado por descarga atmosférica” é codificação genérica do despachante, e não descreve o que a equipe achou</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ETO-RD-GU 00305/2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>INCLUIR</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>QUEIMADO</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SAÍDA</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>O dono mandou mover para queimado: “esses aqui você retira de onde ele tiver e move para queimados”. o caso saía do indicador por estar a 243 horas da janela; o texto da ss declara falha do equipamento, a crítica registra partido na fase e a obra movimentou 1 transformador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>ETO-RD-GU 00685/2026</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>EXCLUIR</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Abalroamento</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>EXCLUÍDA</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>o dono mandou mover para abalroamento, e as quatro vozes concordam com ele: a Crítica registra causa POSTE DE AT e subcausa ABALROADO, o TMAE repete as duas, a SS foi gravada como ABALROAMENTO e a obra 0412600528 entra no SIGCO 20497 — DANOS CAUSADOS POR TERCEIROS. O caso saía como obra de poste por segurança, que é outra coisa: segurança é a companhia decidindo trocar um poste, abalroamento é um terceiro derrubando. A diferença muda para onde o custo vai — ressarcimento, não manutenção</t>
         </is>
